--- a/results/Int Task Remove ACC -0.0/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.0049670024313997144 +/- 0.001203732091084627</t>
+          <t>0.0045501910385550405 +/- 0.000884872469805979</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.004341785342132631 +/- 0.0013828432954077331</t>
+          <t>0.0032997568600208306 +/- 0.0008543503908474476</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.003334491142757945 +/- 0.0014670866329935905</t>
+          <t>-0.0013546370267453977 +/- 0.0015490867051738606</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.002813476901701928 +/- 0.0013403113151493255</t>
+          <t>-0.005105939562348061 +/- 0.001300101929295765</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.003265022577283827 +/- 0.0015235645848878949</t>
+          <t>0.009795067731851325 +/- 0.001714340073532916</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.006460576589093492 +/- 0.0017101123480501895</t>
+          <t>0.010246613407433125 +/- 0.0016962994716324818</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.00027787426189647136 +/- 0.00013893713094823568</t>
+          <t>-0.000416811392844707 +/- 0.00013893713094823568</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.001597777005904777 +/- 0.001539320583963895</t>
+          <t>-0.0028829454671761233 +/- 0.0011525293520692553</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.016116707189996582 +/- 0.0026958816133285483</t>
+          <t>0.021187912469607505 +/- 0.003342441604368031</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.038971865230983026 +/- 0.0029750070309640716</t>
+          <t>0.035845779784647445 +/- 0.003642299889939099</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.007433136505731086 +/- 0.0015856494908667467</t>
+          <t>-0.0051754081278221455 +/- 0.0011773845958095467</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-0.004480722473080878 +/- 0.0017398374138754217</t>
+          <t>0.00027787426189649354 +/- 0.0013162414255989123</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.006217436609933935 +/- 0.001303808570970728</t>
+          <t>0.0026398054880166664 +/- 0.0012542876057844961</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.004133379645710256 +/- 0.0031547066911176186</t>
+          <t>-0.0021535255296978193 +/- 0.0030510859681831034</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.005383813824244588 +/- 0.0020088911067622527</t>
+          <t>0.00041681139284471813 +/- 0.0014963986959734665</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0023619312261202287 +/- 0.001361300308597825</t>
+          <t>-0.0027787426189649135 +/- 0.001643926303049569</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.007328933657519909 +/- 0.0010923365886430275</t>
+          <t>0.0 +/- 0.0012619591611382406</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.008718304967002478 +/- 0.0013221859194633007</t>
+          <t>0.0027440083362278546 +/- 0.0013403113151493576</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>-0.010593956234803702 +/- 0.0010333084251923196</t>
+          <t>0.0029176797499131713 +/- 0.0012828194034469893</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-3.4734282737036715e-05 +/- 0.0002431399791594473</t>
+          <t>3.473428273705892e-05 +/- 0.00010420284821117675</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.006946856547412239 +/- 0.003273141782393803</t>
+          <t>-0.011844390413337957 +/- 0.002264131780164261</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.000382077110107637 +/- 0.0011875874260005926</t>
+          <t>0.0011114970475859741 +/- 0.0012211459417330313</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.002084056964223624 +/- 0.0018313895556045859</t>
+          <t>0.00010420284821118785 +/- 0.0013984593358247564</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0018061827023272525 +/- 0.0009799747120295785</t>
+          <t>-0.0014588398749565967 +/- 0.0011393691883887862</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.0029176797499132047 +/- 0.001593240005721414</t>
+          <t>0.0029176797499131713 +/- 0.0007481993479867182</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.00041681139284478476 +/- 0.0004338310523375149</t>
+          <t>-0.0006599513720041639 +/- 0.0006105729708665097</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.011323376172282096 +/- 0.0037222447584907997</t>
+          <t>0.011010767627648466 +/- 0.0027219358386196863</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.0013893713094823902 +/- 0.002690505971661964</t>
+          <t>0.004272316776658569 +/- 0.0013001019292957963</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.004411253907606838 +/- 0.0010879096744262468</t>
+          <t>0.004376519624869735 +/- 0.001772469721732995</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.011219173324070908 +/- 0.0012431768091819091</t>
+          <t>0.007849947898575859 +/- 0.0020265303432879323</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.0012156998957970843 +/- 0.0006066081693842582</t>
+          <t>-0.00048627995831884707 +/- 0.0006626878787196496</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.0013546370267454421 +/- 0.000610572970866509</t>
+          <t>-0.0013893713094824567 +/- 0.0006213457387981391</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.006530045154567598 +/- 0.0016277005229399161</t>
+          <t>0.006946856547412295 +/- 0.002386323589762798</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.007189996526571663 +/- 0.0017646246329809754</t>
+          <t>-0.004272316776658558 +/- 0.001569205557217996</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-0.0004862799583188027 +/- 0.0005643652938267407</t>
+          <t>-0.0001736714136853168 +/- 0.0005654331572108261</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3.4734282737103325e-05 +/- 0.0005021477004099039</t>
+          <t>-0.001215699895797151 +/- 0.0006451606676278699</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.005105939562348083 +/- 0.0017231145195988219</t>
+          <t>0.0056964223688780735 +/- 0.0018194929980838936</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.0017019798541159648 +/- 0.0017328891536320238</t>
+          <t>0.005904828065300449 +/- 0.001162431436657278</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.0006252170892670384 +/- 0.0005335981763020926</t>
+          <t>-0.001736714136853068 +/- 0.0003804950034770093</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.0011462313303230776 +/- 0.0015223763112755138</t>
+          <t>0.0026745397707537257 +/- 0.0017160985518632267</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.002118791246960805 +/- 0.0012373402661032843</t>
+          <t>-0.0032302882945467125 +/- 0.0015064431012297048</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-0.0007641542202153073 +/- 0.001472012511317641</t>
+          <t>-0.0003820771101076592 +/- 0.001146231330323018</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.002466134074331405 +/- 0.0012077345363469127</t>
+          <t>-0.0009378256339006464 +/- 0.0009952447920732268</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.0004862799583188027 +/- 0.0019289257904709655</t>
+          <t>0.005244876693296263 +/- 0.002642774513598781</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.0020493226814865652 +/- 0.0016101878411252742</t>
+          <t>0.0026398054880166443 +/- 0.0017030428165517525</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.0023619312261201285 +/- 0.002012191505100423</t>
+          <t>0.007780479333101775 +/- 0.0013199027440083447</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.0007294199374782373 +/- 0.0007522197925566967</t>
+          <t>-0.0002084056964223757 +/- 0.0005853525372126567</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.0014241055922194824 +/- 0.0011462313303230163</t>
+          <t>0.001111497047585952 +/- 0.0012790519374450875</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0040291767974991784 +/- 0.0023923828214967332</t>
+          <t>0.0021882598124348673 +/- 0.0015459682587195304</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0010767627648489598 +/- 0.0013932734366190987</t>
+          <t>0.01670718999652655 +/- 0.0013581948451557614</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.008857242097950723 +/- 0.0016676073475731634</t>
+          <t>0.01139284473775617 +/- 0.0019451198332754405</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.0020493226814865873 +/- 0.0009756562629516012</t>
+          <t>-0.002466134074331361 +/- 0.00059048280653005</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>-0.001007294199374742 +/- 0.0009506031388262559</t>
+          <t>0.001910385550538385 +/- 0.0005654331572108228</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-0.00024313997915939022 +/- 0.00031260854463357226</t>
+          <t>0.0 +/- 0.0002196788926827472</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.008614102118791312 +/- 0.0018366521801183977</t>
+          <t>0.0007988885029524218 +/- 0.0011098676838256646</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.0004168113928446959 +/- 0.0018035088552618508</t>
+          <t>0.0020493226814866095 +/- 0.0012176830943354043</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-0.0014588398749565302 +/- 0.0008190223079229874</t>
+          <t>-0.0025356026398055008 +/- 0.0011206853633137762</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-0.00524487669329623 +/- 0.0010472256638889468</t>
+          <t>-0.004550191038555052 +/- 0.0010356409528221875</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.010038207711010827 +/- 0.001247052662106052</t>
+          <t>0.01597777005904828 +/- 0.0015533643469953233</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>-0.002535602639805423 +/- 0.0008515214082758681</t>
+          <t>-0.002466134074331361 +/- 0.0005021477004099024</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-0.0024661340743313163 +/- 0.0015016301716719012</t>
+          <t>0.0021187912469607605 +/- 0.0017741705854980394</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.0025008683570684866 +/- 0.001016237501794223</t>
+          <t>0.008822507815213609 +/- 0.0015703583960343629</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.006147968044459828 +/- 0.0017917638591912425</t>
+          <t>-0.0074678707884682114 +/- 0.001910385550538391</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.00392497394928788 +/- 0.001076762764848891</t>
+          <t>0.00045154567558179924 +/- 0.0012528439594908954</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>-0.00048627995831882485 +/- 0.00023040116640188644</t>
+          <t>0.00010420284821117675 +/- 0.0001591724798525704</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.00944772490448067 +/- 0.0016715817180293132</t>
+          <t>0.001875651267801326 +/- 0.0016672455713789248</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.004063911080236249 +/- 0.0017917638591912486</t>
+          <t>-0.0009725599166377164 +/- 0.002059599455418355</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.002257728377909052 +/- 0.0011855538843957006</t>
+          <t>-0.0029871483153873003 +/- 0.001174820043437844</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.0034039597082319737 +/- 0.0007252731162841516</t>
+          <t>-0.011462313303230299 +/- 0.0015219800139080653</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.0003820771101076259 +/- 0.0014359170968109864</t>
+          <t>-0.0021187912469607605 +/- 0.0011670925749504284</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.003820771101076703 +/- 0.002391374015708011</t>
+          <t>0.0008336227856894918 +/- 0.0017171527744784007</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.00013893713094828008 +/- 0.00017016253857476764</t>
+          <t>-0.00010420284821117675 +/- 0.0001591724798525704</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-0.0024313997915942688 +/- 0.0008923398804213348</t>
+          <t>-0.004793331017714497 +/- 0.001430445313093009</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-0.004411253907606727 +/- 0.001262437085473168</t>
+          <t>-0.002570336922542571 +/- 0.001164505357015673</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,52 +1266,52 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-0.00479333101771443 +/- 0.0010512501528601298</t>
+          <t>0.00020840569642236462 +/- 0.0007152226565464856</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-0.008336227856894718 +/- 0.0010535429585344278</t>
+          <t>-0.0025703369225425488 +/- 0.002491201261138042</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>-0.0018409169850642226 +/- 0.0002224079276635299</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>-0.0002084056964223202 +/- 0.0004168113928447515</t>
+          <t>-0.00013893713094823568 +/- 0.0005853525372126712</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.003195554011809587 +/- 0.0021846731772860502</t>
+          <t>-0.004828065300451545 +/- 0.0013845871085790046</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>-0.0007988885029523551 +/- 0.0013367058982211861</t>
+          <t>0.004758596734977405 +/- 0.0017782460210031513</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.0011462313303229887 +/- 0.0008794017993172524</t>
+          <t>0.0003820771101076703 +/- 0.001103326167021085</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.0002084056964223091 +/- 0.001301493157012506</t>
+          <t>0.0021882598124348786 +/- 0.0016369394467451452</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.008926710663424741 +/- 0.0019590258634531034</t>
+          <t>-0.011184439041333783 +/- 0.0013613003085978035</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.003473428273706092 +/- 0.0011624314366572848</t>
+          <t>-0.005314345258770403 +/- 0.0014492980927422903</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.002431399791594291 +/- 0.001172764363746739</t>
+          <t>0.0012851684612712356 +/- 0.0013367058982211876</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.002466134074331383 +/- 0.0018078518485131214</t>
+          <t>0.0060090309135116034 +/- 0.0014156084662948732</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.003021882598124337 +/- 0.0015144306604092858</t>
+          <t>0.0006946856547412339 +/- 0.0012619591611382347</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.006912122264675214 +/- 0.0011142073589680774</t>
+          <t>-0.00045154567558182147 +/- 0.0010072941993747794</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.4734282737081126e-05 +/- 0.0010356409528222016</t>
+          <t>0.0027092740534907732 +/- 0.0013613003085978256</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-6.946856547410674e-05 +/- 0.0007735692063675055</t>
+          <t>-0.0027787426189649356 +/- 0.0014405308338539694</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.0008336227856894695 +/- 0.00041681139284475326</t>
+          <t>0.00048627995831882485 +/- 0.0003183449597051408</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.002327196943383125 +/- 0.0004124467553677782</t>
+          <t>0.001597777005904788 +/- 0.0009848868967528971</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.009586662035428961 +/- 0.003048712505382666</t>
+          <t>0.0008336227856894585 +/- 0.0035258291185688113</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.001180965613060092 +/- 0.0032256163296266456</t>
+          <t>0.012365404654393841 +/- 0.00343219710372646</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.0037513025356026297 +/- 0.0011393691883887964</t>
+          <t>-0.001424105592219549 +/- 0.0013312794648653499</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.0006599513720041527 +/- 0.0013581948451557564</t>
+          <t>0.0029176797499131267 +/- 0.0009346039629783748</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0012156998957971398 +/- 0.0015318566912955818</t>
+          <t>0.0029524140326501968 +/- 0.0010449189966301594</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.020944772490448082 +/- 0.0031339871576122275</t>
+          <t>0.020284821118443874 +/- 0.001667245571378944</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.00916985064258422 +/- 0.002496039489158969</t>
+          <t>-0.006599513720041717 +/- 0.001784679760842659</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.006252170892671061 +/- 0.001804846273951591</t>
+          <t>-0.004202848211184463 +/- 0.0011356570145378106</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.0007641542202153406 +/- 0.001230986116475834</t>
+          <t>0.0018061827023271749 +/- 0.00138763350854032</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.008232025008683553 +/- 0.0013093488589767785</t>
+          <t>-0.007537339353942385 +/- 0.0014492980927422788</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.0009725599166377164 +/- 0.001128730587653502</t>
+          <t>0.0035428968391802316 +/- 0.0010162375017942246</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.0006946856547412006 +/- 0.00021967889268278236</t>
+          <t>0.0001736714136852946 +/- 0.000388341086748806</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.001354637026745409 +/- 0.0018474589992319745</t>
+          <t>0.005105939562347994 +/- 0.001673385129620833</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.0073984022229940825 +/- 0.0015537526395515845</t>
+          <t>-0.0016672455713789835 +/- 0.0013162414255989048</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-0.0022229940951719483 +/- 0.0008248935107355349</t>
+          <t>0.0020145883987495393 +/- 0.001191137770023081</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.0010072941993747753 +/- 0.0011875874260006203</t>
+          <t>0.0025703369225425154 +/- 0.0013014931570125296</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.0014588398749565633 +/- 0.0011911377700230719</t>
+          <t>0.00020840569642234242 +/- 0.0012250914962520561</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.00024313997915943465 +/- 0.0005822526785078167</t>
+          <t>0.0022229940951719153 +/- 0.0004168113928447514</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.0007641542202153184 +/- 0.0016277005229399046</t>
+          <t>0.0018756512678012927 +/- 0.002609467172072667</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.014762070163251106 +/- 0.002320967540435992</t>
+          <t>-0.00930878777353249 +/- 0.002156884292637728</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.009100382077110091 +/- 0.00216247063789835</t>
+          <t>-0.005071205279611013 +/- 0.0009848868967528776</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.005765890934352191 +/- 0.0016888149748028028</t>
+          <t>-0.0006946856547412672 +/- 0.0011830070417454827</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00024313997915946793 +/- 0.0006599513720041692</t>
+          <t>-0.000138937130948269 +/- 0.00047115873449984956</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.00045154567558179924 +/- 0.00046730198148919525</t>
+          <t>0.00017367141368526128 +/- 0.0006815358412764335</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.006321639458145167 +/- 0.0010626647128015544</t>
+          <t>0.0008683570684265063 +/- 0.0013294657317821901</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.006460576589093436 +/- 0.0022088382209912603</t>
+          <t>-0.004550191038555085 +/- 0.001834351639668084</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3.473428273707002e-05 +/- 0.00045154567558179073</t>
+          <t>-0.00020840569642240902 +/- 0.0007951040737936403</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.0010420284821118675 +/- 0.0006590366780482884</t>
+          <t>0.00024313997915941242 +/- 0.0011420133534403131</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.006425842306356355 +/- 0.0012156998957971654</t>
+          <t>-0.0038555053838138396 +/- 0.0013312794648653514</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.005244876693296286 +/- 0.0019304888130031498</t>
+          <t>-0.0019798541160125247 +/- 0.0016948764013554377</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.0025703369225425488 +/- 0.0004961047883669959</t>
+          <t>0.0011809656130600365 +/- 0.0005643652938267475</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.003438693990969055 +/- 0.0012470526621060143</t>
+          <t>0.0037513025356026184 +/- 0.0019819857752951956</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.010038207711010761 +/- 0.0015799326732260056</t>
+          <t>-0.001945119833275466 +/- 0.0010671963526042022</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0010767627648489153 +/- 0.0015568554936446462</t>
+          <t>0.005418548106981558 +/- 0.000810135726967052</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.00496700243139978 +/- 0.0010654992462784411</t>
+          <t>0.0014241055922194934 +/- 0.0011249833095311986</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-0.002466134074331361 +/- 0.0011142073589680635</t>
+          <t>-3.3306690738754695e-17 +/- 0.0011414850104310482</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.00041681139284471813 +/- 0.0016497870214710567</t>
+          <t>-0.0009030913511636097 +/- 0.0009600746760045257</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.002327196943383114 +/- 0.0009830477039308486</t>
+          <t>0.0012156998957971287 +/- 0.0009976663158280587</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.00010420284821118785 +/- 0.0004673019814891754</t>
+          <t>0.00045154567558176596 +/- 0.0004124467553677333</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.0008683570684265174 +/- 0.0008543503908474409</t>
+          <t>-0.0010420284821118565 +/- 0.0007766821734976715</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.0023966655088572208 +/- 0.0013403113151493392</t>
+          <t>0.00013893713094821348 +/- 0.001319902744008332</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.007155262243834659 +/- 0.0009970614862387774</t>
+          <t>0.0009378256339006241 +/- 0.0011525293520692626</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0001736714136853057 +/- 0.0014838492089818604</t>
+          <t>0.0023966655088571986 +/- 0.001410485620301977</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.0003473428273706003 +/- 0.0010186091211264574</t>
+          <t>0.00038207711010764813 +/- 0.00024313997915941245</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.00024313997915944574 +/- 0.0005392210731594336</t>
+          <t>0.00017367141368526128 +/- 0.0006990139561478977</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.00027787426189647136 +/- 0.00020840569642235354</t>
+          <t>0.00031260854463353025 +/- 0.00028852462184499695</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3.3306690738754695e-17 +/- 0.0009189827409046853</t>
+          <t>-0.001493574157693678 +/- 0.0019713044284352414</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.0010767627648489043 +/- 0.0011033261670210727</t>
+          <t>-0.0037165682528656043 +/- 0.0014984129635375423</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.0010767627648489043 +/- 0.0007024573954899794</t>
+          <t>0.001007294199374753 +/- 0.00045154567558181204</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.0031608197290725836 +/- 0.000857170036766451</t>
+          <t>0.006912122264675224 +/- 0.001247052662106019</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-0.0010767627648489043 +/- 0.0009756562629515985</t>
+          <t>-0.0029871483153873224 +/- 0.0012446316684382609</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.0010420284821118452 +/- 0.0008648766653691182</t>
+          <t>6.946856547410674e-05 +/- 0.0004338310523374936</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.0007294199374782928 +/- 0.001477330345129355</t>
+          <t>-0.0015630427231677845 +/- 0.0012451162437606888</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.0040291767974991125 +/- 0.0010895718750509192</t>
+          <t>0.0038555053838137954 +/- 0.0012470526621060165</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.0016325112886418803 +/- 0.0015223763112755255</t>
+          <t>0.0003473428273705892 +/- 0.0013271950798570873</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.002466134074331372 +/- 0.0016251042119193773</t>
+          <t>0.004237582493921477 +/- 0.000903091351163578</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>-0.0009725599166377274 +/- 0.0005557485237929872</t>
+          <t>0.0006252170892670605 +/- 0.0002084056964223535</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.001493574157693678 +/- 0.0013635141664738077</t>
+          <t>-0.0009378256339006907 +/- 0.0011313996161794087</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.003681833970128512 +/- 0.0006981504425926248</t>
+          <t>0.002882945467176079 +/- 0.001142013353440343</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.0018061827023272193 +/- 0.0006174501158260279</t>
+          <t>-0.0006599513720041972 +/- 0.000702457395489976</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.009829802014588395 +/- 0.0020136898979695203</t>
+          <t>0.0032650225772837605 +/- 0.0022787383767775937</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.0005904828065300572 +/- 0.001398459335824753</t>
+          <t>0.005557485237929804 +/- 0.0008648766653691405</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>-0.0050712052796109686 +/- 0.0013911069395276855</t>
+          <t>0.003577631121917313 +/- 0.001457598836982094</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>6.946856547411784e-05 +/- 0.00020840569642235354</t>
+          <t>0.00024313997915941242 +/- 0.0001591724798525704</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.0007988885029524218 +/- 0.001262437085473173</t>
+          <t>-0.002222994095171971 +/- 0.00144220489697998</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.0019798541160125247 +/- 0.0010192011636763517</t>
+          <t>0.00013893713094821348 +/- 0.0005425668409799632</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-0.004654393886766228 +/- 0.0008676621046750146</t>
+          <t>-0.008440430705105972 +/- 0.0007617822924439455</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.0004168113928447514 +/- 0.0013963008851852518</t>
+          <t>-6.946856547416225e-05 +/- 0.0012309861164758059</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0009030913511636097 +/- 0.0006981504425926202</t>
+          <t>0.0001736714136852946 +/- 0.00035592048509756316</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.00013893713094822457 +/- 0.0009474249181650483</t>
+          <t>0.002049322681486598 +/- 0.000768091156217291</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.0029524140326501968 +/- 0.0014426231092250824</t>
+          <t>-0.00142410559221956 +/- 0.0014526240824124105</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.0015283084404306812 +/- 0.0006806501542989142</t>
+          <t>-0.00027787426189650465 +/- 0.0005557485237929885</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>-0.005800625217089262 +/- 0.0016442932099401879</t>
+          <t>0.003369225425494937 +/- 0.0006223158342191332</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>-6.946856547411784e-05 +/- 0.001085133681959922</t>
+          <t>0.005592219520666864 +/- 0.0010586836161256153</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.00128516846127128 +/- 0.0009455128578545329</t>
+          <t>0.0030913511635984547 +/- 0.0007680911562173152</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.0010380622837370401 +/- 0.0014266801472725688</t>
+          <t>-0.0037370242214533334 +/- 0.0013112315101381623</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.009619377162629717 +/- 0.002431026722525982</t>
+          <t>0.01570934256055362 +/- 0.0011805344020229575</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.000657439446366781 +/- 0.0015354122998154855</t>
+          <t>-0.0021799307958477844 +/- 0.0016598179868805036</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0021453287197231276 +/- 0.0007057466454799408</t>
+          <t>-0.0017301038062284002 +/- 0.0010147320621879173</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.0015224913494809923 +/- 0.0011286855661107502</t>
+          <t>0.0007266435986158948 +/- 0.0015275944674494038</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.006159169550172994 +/- 0.002391301390058261</t>
+          <t>0.010207612456747372 +/- 0.0018456242703244958</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.00013840830449827202 +/- 0.0002295242069450139</t>
+          <t>0.0008304498269896321 +/- 0.00027681660899654404</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.000311418685121112 +/- 0.0007166891064777956</t>
+          <t>-0.0028027681660900083 +/- 0.001640955806419316</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.048719723183390976 +/- 0.0043156987758252935</t>
+          <t>0.0411418685121107 +/- 0.00445400095908476</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.05501730103806226 +/- 0.005071299919878552</t>
+          <t>0.03134948096885809 +/- 0.0056692521353938164</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.000761245674740485 +/- 0.0011137354283343348</t>
+          <t>0.0014532871972318118 +/- 0.000553633217993045</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.0010034602076124499 +/- 0.0015354122998154777</t>
+          <t>-0.002422145328719749 +/- 0.001863378825998106</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.0015570934256055712 +/- 0.001971103857249293</t>
+          <t>-0.0007958477508650752 +/- 0.0033082552602457455</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0023875432525951147 +/- 0.0027133411654138907</t>
+          <t>-0.011141868512110752 +/- 0.005210571760299258</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.009480968858131466 +/- 0.002306689731833756</t>
+          <t>0.00937716262975775 +/- 0.0018009707515118302</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.0024221453287196827 +/- 0.001384083044982673</t>
+          <t>-0.0022491349480969203 +/- 0.0008923042877666314</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.005155709342560588 +/- 0.0019417284216744748</t>
+          <t>0.0005190311418684978 +/- 0.001017677589609168</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.00044982698961938407 +/- 0.0011688128549518888</t>
+          <t>-0.004567474048442943 +/- 0.001561316840509113</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.0029065743944636235 +/- 0.0014367155357803791</t>
+          <t>-0.002871972318339122 +/- 0.001608531390888492</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.4602076124568006e-05 +/- 0.00032643533328916084</t>
+          <t>0.00027681660899654404 +/- 0.00020761245674740802</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.007162629757785444 +/- 0.002076412898086852</t>
+          <t>-0.00916955017301042 +/- 0.0023784994956518365</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.005051903114186818 +/- 0.0013508111623490265</t>
+          <t>0.0020415224913494455 +/- 0.0016841651935830893</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.0010034602076124722 +/- 0.0008539074518514364</t>
+          <t>0.0011764705882352678 +/- 0.0011497057249713295</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0013840830449826868 +/- 0.0012085985603164432</t>
+          <t>-0.00041522491349481604 +/- 0.0008010959794318617</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.001384083044982698 +/- 0.0013578835204393295</t>
+          <t>0.0012110726643598468 +/- 0.0010409417962969547</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.000934256055363325 +/- 0.0004905690961507714</t>
+          <t>-0.00017301038062284002 +/- 0.0002321177831314696</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.0016608996539792086 +/- 0.0016580136402367873</t>
+          <t>0.005986159169550154 +/- 0.0014270996973911139</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.002006920415224889 +/- 0.0017697871076185845</t>
+          <t>-0.009377162629757806 +/- 0.00196013965927593</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.001972318339100376 +/- 0.001304365178198689</t>
+          <t>-0.007474048442906589 +/- 0.001377145241670065</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.007301038062283716 +/- 0.0025960782673913824</t>
+          <t>-0.0017301038062284113 +/- 0.0016809630175074243</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-0.0005536332179930881 +/- 0.0007768146823752247</t>
+          <t>-0.0006574394463667921 +/- 0.0005882352941176561</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.0016955017301037878 +/- 0.0005675162445278798</t>
+          <t>0.0009688581314879041 +/- 0.0002589382274584082</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.0031833910034601565 +/- 0.0017425160293445174</t>
+          <t>0.014463667820069193 +/- 0.001338344609398873</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.0017301038062284002 +/- 0.0014842637086178233</t>
+          <t>-0.0008650519031142112 +/- 0.0015181599286145583</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>6.920415224913601e-05 +/- 0.00045904841389002776</t>
+          <t>-0.0029411764705882804 +/- 0.00090562299849845</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.000622837370242224 +/- 0.0007549281740232445</t>
+          <t>-0.00044982698961938407 +/- 0.0008622792937285331</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.0016955017301037768 +/- 0.0013352097841919965</t>
+          <t>-0.0009688581314879152 +/- 0.0014417070350172788</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.0023183391003459785 +/- 0.0020356492844405055</t>
+          <t>-0.0017301038062284223 +/- 0.0021884274464833023</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.000311418685121112 +/- 0.0006824596167237482</t>
+          <t>-0.001072664359861608 +/- 0.0008397689342222687</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.0035640138408303936 +/- 0.0010501031768507787</t>
+          <t>0.0011072664359861428 +/- 0.0009128654642403149</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0005190311418684756 +/- 0.0029411764705882335</t>
+          <t>-0.003079584775086541 +/- 0.0016115060238332212</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.0007612456747404961 +/- 0.0015224913494809923</t>
+          <t>0.0019377162629757526 +/- 0.0013771452416700331</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.003702422145328754 +/- 0.0018955496089691794</t>
+          <t>-0.004221453287197296 +/- 0.0009513997982607425</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.0059515570934255855 +/- 0.0011866040276458485</t>
+          <t>-0.005294117647058849 +/- 0.0012384449943372252</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0025951557093425114 +/- 0.0012595345829204936</t>
+          <t>0.0034602076124566894 +/- 0.0012760615165803499</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.0005190311418684978 +/- 0.0013512542691879919</t>
+          <t>0.004117647058823481 +/- 0.001141868512110744</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.0008304498269896321 +/- 0.0006033078122547737</t>
+          <t>-0.00038062283737024807 +/- 0.0005460115514899565</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>-0.0014878892733564241 +/- 0.0012189560521666993</t>
+          <t>-0.0004498269896193952 +/- 0.0010614437128150776</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.00041522491349478275 +/- 0.0027148851551464376</t>
+          <t>-0.011314878892733604 +/- 0.001516581799364088</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.0022145328719723524 +/- 0.0013596458618954188</t>
+          <t>-0.006885813148788944 +/- 0.0011626503540768953</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0010034602076124388 +/- 0.0010082216113725306</t>
+          <t>-0.00847750865051906 +/- 0.0019031141868512149</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.00044982698961938407 +/- 0.0005371686746110817</t>
+          <t>0.00010380622837370401 +/- 0.00031141868512111207</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.0006574394463667921 +/- 0.00047569989913037123</t>
+          <t>0.000622837370242224 +/- 0.0004035260826882623</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.001072664359861608 +/- 0.0003612562805851457</t>
+          <t>0.00017301038062284002 +/- 0.0003190153791450875</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.0023183391003459898 +/- 0.001137666589811299</t>
+          <t>-0.0042906574394464105 +/- 0.001377145241670052</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.006643598615916934 +/- 0.0019128408250637164</t>
+          <t>-0.0052249134948097135 +/- 0.001270890496346478</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,147 +2061,147 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.0005882352941176561 +/- 0.0006929060344118026</t>
+          <t>0.00027681660899654404 +/- 0.00030165390612738686</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.006089965397923858 +/- 0.0009932664425195531</t>
+          <t>0.004048442906574357 +/- 0.0016741827547962587</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-0.0019377162629758081 +/- 0.0016391306965158744</t>
+          <t>-0.007854671280276827 +/- 0.001148142562147911</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.0012802768166090162 +/- 0.00022156139229871787</t>
+          <t>-0.00024221453287197602 +/- 0.0005800364918422307</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-0.00048442906574395204 +/- 0.0011286855661107502</t>
+          <t>-0.0031141868512111204 +/- 0.0017231694945313387</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.0028719723183391445 +/- 0.0011164197788859464</t>
+          <t>-0.01993079584775088 +/- 0.001259059197139087</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.0012110726643598801 +/- 0.0017660623052145386</t>
+          <t>0.0007612456747404739 +/- 0.0010586199682199333</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.007093425605536307 +/- 0.0015416380214494992</t>
+          <t>-0.004290657439446399 +/- 0.0014114932909599272</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-3.4602076124568006e-05 +/- 0.00028742643124284435</t>
+          <t>6.920415224913601e-05 +/- 0.00013840830449827202</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-0.00024221453287197602 +/- 0.0007898070733919378</t>
+          <t>-0.008788927335640151 +/- 0.0015412496506103813</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.00858131487889271 +/- 0.0014165736671597519</t>
+          <t>-0.002318339100346056 +/- 0.001137666589811339</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.00024221453287197602 +/- 0.0006929060344118026</t>
+          <t>0.0005190311418684978 +/- 0.0007133400736362466</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.009757785467128 +/- 0.0017425160293445072</t>
+          <t>0.01515570934256052 +/- 0.001906571254526757</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.0009688581314879041 +/- 0.0008447443332687813</t>
+          <t>-0.0015224913494809923 +/- 0.0013858120688236052</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.009377162629757763 +/- 0.001438797431577259</t>
+          <t>0.00013840830449827202 +/- 0.0008643595845534247</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
+          <t>0.00010380622837370401 +/- 0.00027025085383760466</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.000484429065743941 +/- 0.0006954931225688995</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>0.00020761245674740802 +/- 0.0004942165002451875</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>0.001141868512110722 +/- 0.0004390511259670884</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>0.0017647058823529239 +/- 0.0012326306664744947</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>-0.00041522491349481604 +/- 0.0004590484138900278</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>-0.00027681660899655516 +/- 0.0011137354283343279</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>-0.0074740484429066 +/- 0.0015947015393498768</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>-0.00034602076124568004 +/- 0.0005360530582986127</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.00027681660899654404 +/- 0.0010698702307086882</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>-0.0008650519031142001 +/- 0.001017677589609202</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>0.000311418685121112 +/- 0.00010380622837370401</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>6.920415224913601e-05 +/- 0.0005536332179930881</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>0.0026297577854670793 +/- 0.0010743373492221268</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>-0.0005536332179930881 +/- 0.0005178764549168165</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>-0.0017993079584775363 +/- 0.0013020683544793818</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>0.0030449826989618956 +/- 0.001599200001147585</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>0.0006920415224913601 +/- 0.00034602076124568004</t>
-        </is>
-      </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.002318339100346056 +/- 0.0010726643598616083</t>
+          <t>-0.004221453287197263 +/- 0.0012066156245095082</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.0001730103806228289 +/- 0.0016540371491650051</t>
+          <t>-0.0016955017301038323 +/- 0.001527594467449443</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.0008996539792387681 +/- 0.001210578248064787</t>
+          <t>-0.001418685121107288 +/- 0.0010432396838533956</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.003556771545827608 +/- 0.0010507723321297672</t>
+          <t>-0.00030779753761965843 +/- 0.0015780125848234266</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.008036935704514392 +/- 0.001663175980271928</t>
+          <t>0.0026333789329685774 +/- 0.0020973663620330995</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.003522571819425413 +/- 0.002119555462701269</t>
+          <t>-0.00393296853625168 +/- 0.0020477041559401883</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.0019835841313269762 +/- 0.0016948716406790481</t>
+          <t>-0.0006155950752393724 +/- 0.002590163642785413</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.004651162790697649 +/- 0.002064485399833984</t>
+          <t>-0.000683994528043752 +/- 0.001922499223331773</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.004411764705882393 +/- 0.001913046001497538</t>
+          <t>0.005916552667578701 +/- 0.002046561463799907</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.000376196990424138 +/- 0.0002393980848153375</t>
+          <t>-0.00020519835841310564 +/- 0.00016754375805628282</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.008036935704514326 +/- 0.0025558432820155224</t>
+          <t>0.008652530779753798 +/- 0.001418773496080136</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.04001367989056086 +/- 0.004390371145247955</t>
+          <t>0.019630642954856392 +/- 0.0037062153718588563</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.028898768809849474 +/- 0.0027241965897438574</t>
+          <t>0.0266415868673051 +/- 0.001925235013001032</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.004890560875512961 +/- 0.0007654934776196889</t>
+          <t>0.0016415868673051114 +/- 0.0012023526560360478</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.001573187414500654 +/- 0.0013263145984723295</t>
+          <t>-0.00748974008207931 +/- 0.002321806302666718</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.009746922024623772 +/- 0.0013701248716833285</t>
+          <t>0.00047879616963066864 +/- 0.0017249685653787452</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.0062585499316004985 +/- 0.0028492703181724937</t>
+          <t>-0.00400136798905607 +/- 0.0019228033921847494</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.01928864569083445 +/- 0.0030938940842403888</t>
+          <t>0.00974692202462384 +/- 0.00178527813079867</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.004890560875512961 +/- 0.0020749399879777556</t>
+          <t>0.002975376196990465 +/- 0.001940966295986685</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.001778385772913782 +/- 0.0012959846321132806</t>
+          <t>0.011217510259917952 +/- 0.0014331276908178573</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.004103967168262679 +/- 0.0023545710640298875</t>
+          <t>-0.0041039671682626235 +/- 0.0017371306565253572</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.005300957592339217 +/- 0.0005567312105369102</t>
+          <t>0.007489740082079388 +/- 0.0022553675914907686</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.0005813953488371992 +/- 0.00040609925058268344</t>
+          <t>-0.00020519835841310564 +/- 0.00034877014456858744</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.008618331053351547 +/- 0.0023486025599711775</t>
+          <t>0.006019151846785253 +/- 0.0018109715861660547</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.004445964432284599 +/- 0.001618626479644206</t>
+          <t>-0.00283857729138165 +/- 0.0010927869568173976</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.010841313269493802 +/- 0.0017508790336757951</t>
+          <t>0.0028727770177838785 +/- 0.0015386076442136674</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.003625170998631999 +/- 0.0011866861540969446</t>
+          <t>0.00041039671682627785 +/- 0.0011827371043632577</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.0023597811217510476 +/- 0.0007083555122164288</t>
+          <t>0.0017783857729138596 +/- 0.00204513220078331</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0007181942544459252 +/- 0.0004944197091245046</t>
+          <t>0.0009575923392613373 +/- 0.000588394341110975</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.005642954856361182 +/- 0.001444913144615438</t>
+          <t>-0.0020519835841312896 +/- 0.0024134444274113826</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.003625170998631988 +/- 0.0020128507482301155</t>
+          <t>0.002393980848153232 +/- 0.00250383108313585</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.006463748290013715 +/- 0.0021815565572936998</t>
+          <t>-0.005574555403556725 +/- 0.0014021887824897297</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.00926812585499318 +/- 0.002341869810638837</t>
+          <t>-0.00400136798905606 +/- 0.0012800935206711988</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.00109439124487003 +/- 0.0005883943411109711</t>
+          <t>0.001162790697674465 +/- 0.0007042154679197651</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.0005813953488371882 +/- 0.0006127384701494062</t>
+          <t>0.0009233926128591419 +/- 0.00037619699042407243</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.0035567715458276637 +/- 0.0021148597583776083</t>
+          <t>-0.004890560875512972 +/- 0.0016827516552862572</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.0002393980848152788 +/- 0.0013769372188233426</t>
+          <t>0.001265389876881029 +/- 0.001640517777730706</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.0032489740082079057 +/- 0.0011470936957078306</t>
+          <t>0.00010259917920660833 +/- 0.0008243482074687966</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.002017783857729105 +/- 0.0005609172184287673</t>
+          <t>-0.0007181942544459252 +/- 0.0007865937072503469</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.002120383036935758 +/- 0.0012406537036400312</t>
+          <t>0.0007181942544459919 +/- 0.0011076699549043406</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.0039671682626539195 +/- 0.0012905582943989757</t>
+          <t>-0.0006155950752393391 +/- 0.0011218344368575175</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.000991792065663455 +/- 0.0006203268518200065</t>
+          <t>0.0012995896032832466 +/- 0.0006268913399392379</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.005574555403556813 +/- 0.0013425298513262992</t>
+          <t>0.0009233926128591307 +/- 0.001867254951397913</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.010943912448700455 +/- 0.001958662252158201</t>
+          <t>-0.012106703146374798 +/- 0.001476541254782693</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.002154582763337931 +/- 0.0014753525725118369</t>
+          <t>0.00170998632010948 +/- 0.0013934027898401687</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0026675786593707063 +/- 0.0017086177834195223</t>
+          <t>-0.004685362517099822 +/- 0.0016405177777306847</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.003967168262653887 +/- 0.0016486964149376056</t>
+          <t>-0.0009233926128590642 +/- 0.0011244379085344506</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.0034541723666211 +/- 0.0007562703278897481</t>
+          <t>0.0007523939808481872 +/- 0.0009403370099088625</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.0009575923392613261 +/- 0.001172806306394135</t>
+          <t>-0.005232558139534859 +/- 0.001003515783250421</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.0004787961696306908 +/- 0.00046390765958449596</t>
+          <t>-0.0016415868673050448 +/- 0.00045371064163548933</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.004411764705882326 +/- 0.0011181793929050474</t>
+          <t>0.00417236662106707 +/- 0.001132212404736436</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0028727770177838343 +/- 0.0016976297737333551</t>
+          <t>-0.017065663474692162 +/- 0.0023716468464549615</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.0034883720930233065 +/- 0.0018844018213345969</t>
+          <t>-0.0009575923392612373 +/- 0.0026304903588275455</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.00865253077975372 +/- 0.0017773989685617342</t>
+          <t>-0.007763337893296829 +/- 0.0016896880064344083</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-0.0013679890560875819 +/- 0.0005722708799822653</t>
+          <t>-0.002291381668946613 +/- 0.0010035157832504217</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>-0.00017099863201095467 +/- 0.0004651665700661997</t>
+          <t>-0.0011969904240765605 +/- 0.0005129958960328455</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.00010259917920653061 +/- 0.00034370299661837803</t>
+          <t>-0.0029753761969903867 +/- 0.0004848648043350785</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.002701778385772946 +/- 0.003010547349751259</t>
+          <t>-0.0026675786593706842 +/- 0.0021291904810223613</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.0008207934336525002 +/- 0.0018366240194388</t>
+          <t>-0.013337893296853597 +/- 0.0012235666087550086</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.0015047879616962856 +/- 0.0004639076595844763</t>
+          <t>0.00010259917920661943 +/- 0.0005309225272318708</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0013337893296853198 +/- 0.001371831129967968</t>
+          <t>0.00170998632010948 +/- 0.0011747991817590746</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.0011969904240765827 +/- 0.002404948494083343</t>
+          <t>-0.002257181942544417 +/- 0.0008678917606326447</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.0012653898768809513 +/- 0.0003761969904240633</t>
+          <t>-0.001573187414500643 +/- 0.0006701750322252163</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-0.002393980848153254 +/- 0.0017638573130270326</t>
+          <t>-0.002633378932968522 +/- 0.001082030917890307</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.0006497948016416233 +/- 0.001955375151699427</t>
+          <t>0.001573187414500743 +/- 0.0017914912248575602</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-0.0038303693570451826 +/- 0.0014084309358395222</t>
+          <t>0.0015389876880985364 +/- 0.00132675545425929</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.011833105335157346 +/- 0.0009452992449442764</t>
+          <t>-0.00044459644322841774 +/- 0.0015221759975559551</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.0015389876880984698 +/- 0.00046516657006619557</t>
+          <t>0.002017783857729172 +/- 0.0004701685049544297</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.006053351573187449 +/- 0.0018292857893729556</t>
+          <t>-3.4199726402150964e-05 +/- 0.001138907373826712</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.0016415868673050338 +/- 0.0007141112523194507</t>
+          <t>0.005506155950752434 +/- 0.0011181793929050511</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-0.0002735978112175519 +/- 0.001000597731759773</t>
+          <t>-0.0004103967168262113 +/- 0.00039883391893605254</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.0016415868673050893 +/- 0.0014654093902618675</t>
+          <t>0.012551299589603316 +/- 0.0014594109639775577</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.0022571819425444505 +/- 0.0014844414784001745</t>
+          <t>-0.004719562243502029 +/- 0.0012959846321133257</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.002428180574555372 +/- 0.0009727402635655096</t>
+          <t>-0.010362517099863156 +/- 0.001175296872601881</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.0003761969904240603 +/- 0.00023939808481533272</t>
+          <t>-3.419972640217317e-05 +/- 0.00018417116303469415</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.0006497948016415678 +/- 0.0005609172184287639</t>
+          <t>0.0023939808481532434 +/- 0.000904839709666415</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.0014705882352941014 +/- 0.000631538485383684</t>
+          <t>0.00034199726402195374 +/- 0.00043259612314206235</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,52 +2601,52 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>6.839945280434634e-05 +/- 0.0009151223091832922</t>
+          <t>-0.00400136798905606 +/- 0.000918312009719404</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.0014363885088919059 +/- 0.0011925852102710448</t>
+          <t>-0.0010943912448700076 +/- 0.0018276866232404087</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>6.839945280439075e-05 +/- 0.00013679890560878153</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0015047879616962635 +/- 0.0007042154679197738</t>
+          <t>0.00126538987688104 +/- 0.0007342992665384329</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.001470588235294168 +/- 0.0008924752633857643</t>
+          <t>-0.0013337893296853198 +/- 0.0008845770968794589</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.0011285909712721808 +/- 0.0011852068024051788</t>
+          <t>0.001573187414500732 +/- 0.0010282692461267323</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>-6.839945280440185e-05 +/- 0.0006805659624532358</t>
+          <t>0.0022229822161423107 +/- 0.0009582028540438862</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.006190150478796186 +/- 0.0014055213808505137</t>
+          <t>-0.0029411764705882027 +/- 0.001492299878883151</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.0027359781121751416 +/- 0.001059639766404218</t>
+          <t>0.00786593707250346 +/- 0.0011945450886848869</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.0008549931600547511 +/- 0.000933470866207678</t>
+          <t>0.001504787961696341 +/- 0.0009202205230556583</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.005996649916247954 +/- 0.0013437970599753507</t>
+          <t>0.006834170854271349 +/- 0.0013163740505452908</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.0037855946398659412 +/- 0.001734618889916198</t>
+          <t>-0.0011055276381909617 +/- 0.0022674400347092454</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.010050251256281473 +/- 0.0017663552866283617</t>
+          <t>0.008676716917922956 +/- 0.0009045226130653505</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0016080402010050677 +/- 0.0016737013061034253</t>
+          <t>0.00020100502512564454 +/- 0.001341707497118995</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.011490787269681824 +/- 0.0007347307269501471</t>
+          <t>0.011088777219430478 +/- 0.0010428396928826224</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.005628140703517648 +/- 0.0012245002936346412</t>
+          <t>0.010452261306532661 +/- 0.0025723757213336625</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.700167504187781e-05 +/- 0.00013400335008375563</t>
+          <t>-0.00023450586264657237 +/- 0.00021451002470462371</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.004589614740368553 +/- 0.0006186326737895679</t>
+          <t>0.00227805695142379 +/- 0.002117719347307071</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.026130653266331728 +/- 0.003055746532929023</t>
+          <t>0.017554438860971543 +/- 0.0023219729917807173</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.03755443886097158 +/- 0.0025489272444391615</t>
+          <t>0.037018425460636516 +/- 0.003453187291137081</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.000770519262981606 +/- 0.0008481734607150476</t>
+          <t>-0.0010385259631490729 +/- 0.0015238278613794512</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.007236180904522671 +/- 0.0015145935752706706</t>
+          <t>0.006934673366834165 +/- 0.0016551583687819719</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.010519262981574583 +/- 0.0011720506321297155</t>
+          <t>0.002646566164154096 +/- 0.0007705192629815529</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.002579564489112174 +/- 0.004352660051122159</t>
+          <t>0.011155778894472357 +/- 0.0033435447069799108</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.014706867671691848 +/- 0.00259690920955223</t>
+          <t>0.013701842546063648 +/- 0.0016442735265404412</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.004589614740368553 +/- 0.0009943599383353838</t>
+          <t>0.00938023450586265 +/- 0.0013893763050805915</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.0009380234505862895 +/- 0.0006320925381612632</t>
+          <t>0.002613065326633157 +/- 0.0008710217755443715</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.00495812395309877 +/- 0.001427623166007534</t>
+          <t>-0.007202680067001676 +/- 0.001824181358802282</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.008107202680067071 +/- 0.0008710217755443715</t>
+          <t>0.0009715242881072061 +/- 0.001440536013400344</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-6.700167504185562e-05 +/- 0.00013400335008371123</t>
+          <t>0.00046901172529314474 +/- 0.0003070402475682386</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.00525963149078722 +/- 0.0022123238835643553</t>
+          <t>-0.014941373534338364 +/- 0.001422898531430159</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.00016750418760475005 +/- 0.0011236522499998827</t>
+          <t>0.0036180904522613243 +/- 0.0019465110949861114</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0005025125628141169 +/- 0.001062034672304672</t>
+          <t>0.00020100502512564454 +/- 0.0011720506321297155</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0023115577889447846 +/- 0.0017436534244118203</t>
+          <t>0.00197654941373534 +/- 0.000725507799923177</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.0004355108877721503 +/- 0.0012359039695609081</t>
+          <t>0.006398659966499165 +/- 0.0011934012147776633</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0020435510887772735 +/- 0.0004355108877722058</t>
+          <t>0.0007035175879397171 +/- 0.00034975901202381326</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.0019765494137352958 +/- 0.0018192527949595233</t>
+          <t>0.0011055276381909506 +/- 0.002838887142697533</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.00010050251256276122 +/- 0.0014910695533847712</t>
+          <t>-0.00542713567839197 +/- 0.0017777553315137691</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.003986599664991675 +/- 0.0010428396928826216</t>
+          <t>-0.0035845896147403745 +/- 0.0016069929588223104</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0007370184254606782 +/- 0.0015627341761729472</t>
+          <t>0.002747068676716924 +/- 0.0021906576514936975</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.001105527638190984 +/- 0.0008869817282997707</t>
+          <t>-0.00013400335008375563 +/- 0.000373049538548085</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.350083752097221e-05 +/- 0.00031604626908059277</t>
+          <t>-0.00013400335008376674 +/- 0.00104014570829213</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.00043551088777223914 +/- 0.0021919380640476405</t>
+          <t>0.006968174204355105 +/- 0.0020640431223784934</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.0036515912897822854 +/- 0.0014090278622990282</t>
+          <t>0.002981574539363463 +/- 0.0016236677810455946</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-0.0002680067001674336 +/- 0.00029205353055545343</t>
+          <t>0.0005025125628140836 +/- 0.0006573338985041575</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.0005360134003349448 +/- 0.00042902004940920585</t>
+          <t>-0.00020100502512563346 +/- 0.0004020100502512669</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0037185929648241634 +/- 0.0010641460753278563</t>
+          <t>0.004422110552763814 +/- 0.0011966881808704766</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.0013735343383583954 +/- 0.0012927156704572826</t>
+          <t>-0.006666666666666665 +/- 0.0014248690330409843</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.0005025125628140281 +/- 0.0008102771606329979</t>
+          <t>0.00013400335008375563 +/- 0.0011624356162745681</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.0011390284757119117 +/- 0.0013248723573390463</t>
+          <t>0.0025795644891122294 +/- 0.0013404521958956374</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0020100502512563345 +/- 0.0011110970821961432</t>
+          <t>0.0005360134003350225 +/- 0.0010072560387519801</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0033500837520938687 +/- 0.0013974307279473533</t>
+          <t>-0.00010050251256281673 +/- 0.0016069929588223089</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0006700167504188004 +/- 0.0018040753122728784</t>
+          <t>-0.003350083752093802 +/- 0.0016411991576436842</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.007236180904522671 +/- 0.002307427183614414</t>
+          <t>0.00596314907872697 +/- 0.002025623645940509</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.00013400335008368903 +/- 0.0011527404042938059</t>
+          <t>0.0019095477386934846 +/- 0.0004250779745543912</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.004589614740368564 +/- 0.0011316144558830322</t>
+          <t>0.0022445561139028515 +/- 0.001397832230822435</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0004020100502512669 +/- 0.0002506973123466694</t>
+          <t>-0.0005695142378559614 +/- 0.0004749563443470084</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.00010050251256275012 +/- 0.0008613038614527299</t>
+          <t>-0.0021105527638190956 +/- 0.0015573385995536885</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.006767169179229526 +/- 0.0016870590702866642</t>
+          <t>0.004020100502512558 +/- 0.001527873266464508</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0017420435510888121 +/- 0.0014740368509212872</t>
+          <t>-0.0031825795644891074 +/- 0.0013833047116959922</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0003685092127303613 +/- 0.001221288183152969</t>
+          <t>-0.00455611390284758 +/- 0.0014694614539002536</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.0010050251256281783 +/- 0.0007027194962614002</t>
+          <t>0.001407035175879412 +/- 0.0008580400988184662</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.00016750418760471674 +/- 0.00045566065355895575</t>
+          <t>0.0009380234505862783 +/- 0.000683285696963847</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.00010050251256275012 +/- 0.0004749563443469598</t>
+          <t>-0.0005360134003350225 +/- 0.000373049538548085</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.00016750418760461683 +/- 0.0012467533712514705</t>
+          <t>-0.006164154103852603 +/- 0.0019080778379763055</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.0019430485762144567 +/- 0.0012606289931140556</t>
+          <t>-0.0005695142378559614 +/- 0.0008613038614527826</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,92 +2951,92 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4.4408920985006264e-17 +/- 0.0003350083752093447</t>
+          <t>-0.00026800670016751126 +/- 0.0003608150624545827</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-0.004991624790619709 +/- 0.001193401214777672</t>
+          <t>0.0007035175879397171 +/- 0.0006258472928733635</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-0.0023785594639865403 +/- 0.0014560344262714163</t>
+          <t>-0.002646566164154096 +/- 0.0009528618193184312</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.0004355108877722058 +/- 0.0003366792502888159</t>
+          <t>0.001373534338358484 +/- 0.0006775125097539948</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.00026800670016744463 +/- 0.0006666582493176402</t>
+          <t>-0.0005360134003350225 +/- 0.0012097467393814582</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.005929648241205987 +/- 0.0014835236063976314</t>
+          <t>0.0004355108877721947 +/- 0.0011014594454119727</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0.003082077051926335 +/- 0.0021070934932685176</t>
+          <t>0.005460636515912909 +/- 0.002595179954018676</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.0013735343383585064 +/- 0.001183959601143881</t>
+          <t>0.006365159128978215 +/- 0.0007339665762212969</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-0.00020100502512557795 +/- 0.00022221941643917845</t>
+          <t>0.0 +/- 0.0002118779001787915</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.00361809045226138 +/- 0.0009211207427046819</t>
+          <t>0.004924623115577909 +/- 0.0013065326633165777</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.551115123125783e-17 +/- 0.0006865628653908972</t>
+          <t>0.0099497487437186 +/- 0.0014217149195258213</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.0003685092127303502 +/- 0.000506959663330688</t>
+          <t>-0.0005360134003350225 +/- 0.0011910478281160232</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.015175879396984959 +/- 0.0016415410385259633</t>
+          <t>0.0015410385259631565 +/- 0.0012641850763224877</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0.0006365159128978726 +/- 0.0011355746235630231</t>
+          <t>0.006331658291457265 +/- 0.0009645681774799153</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.006901172529313293 +/- 0.001696346921430121</t>
+          <t>0.021407035175879385 +/- 0.0012575091711305502</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>-0.00023450586264650575 +/- 0.00021451002470457514</t>
+          <t>0.00020100502512563346 +/- 0.00016411991576437138</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.001876046901172579 +/- 0.00026800670016751126</t>
+          <t>0.0006700167504187782 +/- 0.0004968977210784496</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.0010385259631491063 +/- 0.0005888909826213538</t>
+          <t>0.002311557788944729 +/- 0.0005888909826213064</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.0009715242881071174 +/- 0.0004355108877722058</t>
+          <t>-0.001072026800670045 +/- 0.0003608150624545827</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.0035510887772195023 +/- 0.001799091669292817</t>
+          <t>0.00395309882747068 +/- 0.0014432602498182917</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3061,37 +3061,37 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.00014982029999996505</t>
+          <t>0.0012060301507537895 +/- 0.0006391552438304465</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0012060301507538008 +/- 0.0005645661489565548</t>
+          <t>0.0021775544388609623 +/- 0.0009265873826424816</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.0020770519262981015 +/- 0.000980150005918136</t>
+          <t>-0.00023450586264657237 +/- 0.0007498502273232825</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.0014405360134003731 +/- 0.0006539102611706416</t>
+          <t>0.001105527638190973 +/- 0.0007035175879396869</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.0012730318257956007 +/- 0.0011966881808704623</t>
+          <t>0.004656616415410398 +/- 0.0007991196275964407</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-3.35008375209056e-05 +/- 0.0009875646883070958</t>
+          <t>0.006532663316582909 +/- 0.0012286178104450288</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>0.001474036850921312 +/- 0.0008761605916664903</t>
+          <t>-0.0003350083752093891 +/- 0.0006177249217616839</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.000645161290322549 +/- 0.0010402913223611038</t>
+          <t>0.0017096774193548936 +/- 0.0016640284356811597</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.0035161290322580528 +/- 0.0014020202459419941</t>
+          <t>0.007258064516129104 +/- 0.0007667654402583648</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.0014193548387096855 +/- 0.0012087092900125848</t>
+          <t>0.010064516129032308 +/- 0.001426667379838451</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.006838709677419374 +/- 0.001389719950228275</t>
+          <t>0.0014838709677419848 +/- 0.0016524191580471824</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.0014193548387096966 +/- 0.0017502787053226617</t>
+          <t>0.004096774193548436 +/- 0.0015674233049363024</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.001483870967741907 +/- 0.0019579343103862568</t>
+          <t>0.02035483870967747 +/- 0.0022323419711994595</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.0013870967741935526 +/- 0.0006618801460865629</t>
+          <t>-9.67741935483435e-05 +/- 0.0005211449813355754</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.003741935483870973 +/- 0.0017383475593945206</t>
+          <t>-0.006322580645161247 +/- 0.001581632344791154</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.01216129032258062 +/- 0.0024947395227077726</t>
+          <t>0.017709677419354884 +/- 0.00314230639660018</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.022064516129032218 +/- 0.0029218043546385174</t>
+          <t>0.03370967741935488 +/- 0.003312543561844197</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.0010967741935483776 +/- 0.002010378896888114</t>
+          <t>0.007419354838709735 +/- 0.0027219384657714775</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.001935483870967769 +/- 0.0012822327041517353</t>
+          <t>0.0015483870967742397 +/- 0.0018631650423475653</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.0009354838709677571 +/- 0.0012194231078345595</t>
+          <t>0.010000000000000054 +/- 0.0016511592118799575</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.02141935483870965 +/- 0.0022955415322138254</t>
+          <t>0.03051612903225811 +/- 0.0019947903011277852</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.005032258064516159 +/- 0.002656936810577298</t>
+          <t>-0.007161290322580604 +/- 0.0017419354838709776</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.00454838709677422 +/- 0.0018779070423003681</t>
+          <t>0.006903225806451652 +/- 0.0019311780060768681</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.003290322580645144 +/- 0.0018463339382263535</t>
+          <t>0.014096774193548444 +/- 0.0018922592743306345</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.003387096774193565 +/- 0.0013930853472057683</t>
+          <t>-0.002387096774193498 +/- 0.0013237602921731214</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.0015161290322580402 +/- 0.0014644592855246666</t>
+          <t>0.01058064516129037 +/- 0.0017478989915024425</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.0009032258064516241 +/- 0.0003761904448287201</t>
+          <t>0.0011612903225806993 +/- 0.0006154446460754652</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.019064516129032216 +/- 0.0027653647961480843</t>
+          <t>0.016354838709677477 +/- 0.00199921941062532</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.0025161290322580853 +/- 0.0016435792519815403</t>
+          <t>-0.0026129032258063955 +/- 0.0018101919802062153</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-0.004548387096774209 +/- 0.0013795745019576301</t>
+          <t>0.002935483870967781 +/- 0.0019645664488497</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.0010645161290322668 +/- 0.001978290078253156</t>
+          <t>0.0028064516129032826 +/- 0.000901496039514968</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.003935483870967727 +/- 0.001344043010064481</t>
+          <t>0.009161290322580706 +/- 0.002046290519632735</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0015483870967742063 +/- 0.00034742998755706424</t>
+          <t>0.0007741935483871365 +/- 0.00035921060405354416</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.00570967741935482 +/- 0.001946474173102658</t>
+          <t>0.013935483870967791 +/- 0.0020340493897334612</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.006193548387096792 +/- 0.0019344083032987326</t>
+          <t>0.000419354838709729 +/- 0.0022397877853986992</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.000225806451612931 +/- 0.0024098738962090188</t>
+          <t>-0.0027419354838709165 +/- 0.0023803304276610836</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.010516129032258103 +/- 0.003223224773366918</t>
+          <t>-0.007935483870967697 +/- 0.0014295819229780797</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.0004193548387096957 +/- 0.0005956833971812351</t>
+          <t>0.0015806451612903616 +/- 0.00033678408093259306</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.0008064516129032362 +/- 0.0006804846164428753</t>
+          <t>0.0008064516129032584 +/- 0.0007391251120896456</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,217 +3271,217 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.0013225806451612975 +/- 0.0015832762828139422</t>
+          <t>-0.016419354838709634 +/- 0.002650074115940745</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.006709677419354865 +/- 0.002008307408551415</t>
+          <t>-0.01083870967741929 +/- 0.002015548303459773</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.0008709677419354578 +/- 0.0005007798289116137</t>
+          <t>0.004129032258064547 +/- 0.0007741935483870829</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.0008387096774193137 +/- 0.0009481895778515515</t>
+          <t>0.0008387096774194025 +/- 0.0007096774193548553</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.010999999999999954 +/- 0.0008343559455727611</t>
+          <t>0.004096774193548447 +/- 0.0009465419839432916</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.0029677419354838808 +/- 0.002408794155173497</t>
+          <t>-0.0028387096774192934 +/- 0.001618056284385105</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.0005161290322580392 +/- 0.0009481895778515441</t>
+          <t>0.0017096774193548826 +/- 0.001020599485132674</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.0018709677419354587 +/- 0.001077631812160627</t>
+          <t>-0.0028064516129031824 +/- 0.001361351473936072</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.010032258064516141 +/- 0.003418289547993704</t>
+          <t>-0.011645161290322514 +/- 0.0013099316454352992</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.001612903225806417 +/- 0.0011540996012902227</t>
+          <t>0.002096774193548445 +/- 0.001627354613629609</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.0006129032258064715 +/- 0.0019054115387899784</t>
+          <t>0.006709677419354909 +/- 0.001806451612903223</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.0023870967741935313 +/- 0.0011826001793434433</t>
+          <t>-0.0002258064516128533 +/- 0.0011635283094755561</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0011935483870967433 +/- 0.0010896352099390154</t>
+          <t>-0.003161290322580601 +/- 0.0012559949892859113</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.0002258064516129199 +/- 0.002065775825365854</t>
+          <t>0.003225806451612945 +/- 0.0021591226491201954</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.0011612903225806214 +/- 0.0007241917522788323</t>
+          <t>-0.0009032258064515575 +/- 0.0010382888348019848</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>0.0005483870967741722 +/- 0.0010507417725743491</t>
+          <t>0.0002903225806452192 +/- 0.0016602721590268002</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0001290322580644987 +/- 0.002569330032482576</t>
+          <t>-0.010354838709677372 +/- 0.002122423761238189</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.008645161290322589 +/- 0.0013897199502282574</t>
+          <t>-0.0023548387096773648 +/- 0.0015064896037207372</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0050645161290322595 +/- 0.0016067625039241705</t>
+          <t>-0.010451612903225748 +/- 0.0021887994133790354</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-0.0015806451612903282 +/- 0.0007277751079147478</t>
+          <t>-0.0022580645161289657 +/- 0.0007496096799111336</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>-0.0016774193548387383 +/- 0.0005734318978913501</t>
+          <t>0.0003225806451613411 +/- 0.0007496096799111192</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.0004997397866073984</t>
+          <t>-0.00035483870967737416 +/- 0.0003937598585720652</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.00406451612903227 +/- 0.0012258064516128973</t>
+          <t>-0.006354838709677335 +/- 0.002444173772840588</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.005354838709677445 +/- 0.0026764475500247235</t>
+          <t>-0.009999999999999953 +/- 0.0013685937700384826</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>3.22580645161219e-05 +/- 9.677419354836571e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0.000709677419354815 +/- 0.0010077741517298977</t>
+          <t>0.0005806451612903829 +/- 0.0010967741935483974</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>0.0010645161290322557 +/- 0.0016826840459025709</t>
+          <t>-0.002161290322580578 +/- 0.002183325323744216</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>0.0005161290322580503 +/- 0.001814498207796785</t>
+          <t>-0.0010967741935483221 +/- 0.001581632344791149</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.001774193548387082 +/- 0.0007530720987050712</t>
+          <t>-0.0003548387096773964 +/- 0.0008090281421925457</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.004612903225806431 +/- 0.002235137058234831</t>
+          <t>0.0010322580645161783 +/- 0.0016498983035541186</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.004225806451612924 +/- 0.002092800204297883</t>
+          <t>-0.0065806451612902776 +/- 0.0018259318320109543</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.0053225806451613015 +/- 0.002081832619388718</t>
+          <t>-0.003032258064516069 +/- 0.002331523999947449</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>0.0019677419354838356 +/- 0.002578426465599025</t>
+          <t>-0.0003548387096773964 +/- 0.0012777614400218287</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-3.2258064516155204e-05 +/- 0.00048815309517488876</t>
+          <t>-0.00019354838709672028 +/- 0.00032896900087695294</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.001000000000000023 +/- 0.0021224237612381992</t>
+          <t>0.01119354838709682 +/- 0.0014357556828559995</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.0069032258064516405 +/- 0.0012757238666635535</t>
+          <t>0.0016129032258065056 +/- 0.0008534681648595538</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.0013225806451612533 +/- 0.0009061014132379523</t>
+          <t>0.001258064516129087 +/- 0.001044782886496886</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.0005483870967741722 +/- 0.0017963426828807461</t>
+          <t>0.018580645161290377 +/- 0.002532617603405241</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-0.006903225806451629 +/- 0.001182600179343467</t>
+          <t>-0.00403225806451607 +/- 0.0016080572362083202</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>0.0004516129032257843 +/- 0.001032258064516127</t>
+          <t>0.013677419354838748 +/- 0.002309100666861083</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>0.00032258064516125227 +/- 0.00028852490032255177</t>
+          <t>-9.67741935483657e-05 +/- 0.00025194353793245967</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.0013225806451612643 +/- 0.0008090281421925638</t>
+          <t>-0.0010322580645160452 +/- 0.0004740947889257803</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.0002580645161290529 +/- 0.0006735681618651776</t>
+          <t>0.00016129032258069831 +/- 0.0009704263842897549</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,52 +3491,52 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.0031612903225806234 +/- 0.0009869070026308545</t>
+          <t>0.004580645161290364 +/- 0.0011878679122272326</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-0.0035806451612903412 +/- 0.0016028720321038532</t>
+          <t>-0.003096774193548335 +/- 0.0017562138824279015</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>3.22580645161219e-05 +/- 9.677419354836571e-05</t>
+          <t>-3.22580645161219e-05 +/- 9.677419354836571e-05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-0.0008387096774193692 +/- 0.0008679757449724879</t>
+          <t>0.0021290322580645783 +/- 0.0007384208478877282</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.0009032258064516352 +/- 0.0008006241061929513</t>
+          <t>0.0006451612903226378 +/- 0.0018864763248017317</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.005548387096774199 +/- 0.0012724569627945814</t>
+          <t>0.0009354838709677904 +/- 0.0011216347516589573</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0025806451612903404 +/- 0.0010601081758164627</t>
+          <t>-0.0035483870967741526 +/- 0.0006120537406777617</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>0.010096774193548364 +/- 0.0018421021335831168</t>
+          <t>0.002064516129032323 +/- 0.002798096573187277</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>0.0028064516129032045 +/- 0.0010703651627765691</t>
+          <t>0.008225806451612961 +/- 0.002207969672083575</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.0007419354838709813 +/- 0.0013840927711564496</t>
+          <t>-0.004096774193548325 +/- 0.0017434282731447284</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0019731943410275345 +/- 0.0019491645737466107</t>
+          <t>0.0020104244229337486 +/- 0.0010017590504150197</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.0007073715562174177 +/- 0.0014269372968530726</t>
+          <t>0.004988830975428149 +/- 0.0026124802372075712</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.0012658227848101444 +/- 0.0013950107219058258</t>
+          <t>0.0006701414743112477 +/- 0.0008122644910376553</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0038719285182427345 +/- 0.0012370251471210778</t>
+          <t>0.00498883097542816 +/- 0.0009593521017665818</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.005919583023082669 +/- 0.0015026385756225261</t>
+          <t>-0.001154132539091568 +/- 0.0013875387307210817</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.00037230081906182156 +/- 0.001614257884488378</t>
+          <t>0.0027550260610573474 +/- 0.0022101000863225377</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.446016381235099e-05 +/- 0.0004009802536957839</t>
+          <t>-7.446016381236209e-05 +/- 0.0002786044219489223</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0055100521221146505 +/- 0.0018375223647435692</t>
+          <t>0.00599404318689502 +/- 0.0016266606310464213</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.014631422189128801 +/- 0.00335504806951775</t>
+          <t>0.02103499627699183 +/- 0.003259493139331471</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.014966492926284436 +/- 0.0029587962004922553</t>
+          <t>0.023641102010424436 +/- 0.0028316897795690912</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-7.446016381237874e-05 +/- 0.0023297822557203354</t>
+          <t>0.00439314966492928 +/- 0.0013088902331531557</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.0037230081906180325 +/- 0.001091800320075587</t>
+          <t>-0.0010796723752792114 +/- 0.0010189078319734824</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.00029784065524945393 +/- 0.0017125837676842835</t>
+          <t>-0.0007446016381235987 +/- 0.001352636047995909</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.00718540580789277 +/- 0.0010667571691656272</t>
+          <t>0.015450483991064783 +/- 0.001964746805950669</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-0.0028294862248697096 +/- 0.002253573484798447</t>
+          <t>0.00517498138495906 +/- 0.0019871937669519706</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.006664184661206269 +/- 0.0012945151638655082</t>
+          <t>0.003536857781087138 +/- 0.0013855393943356911</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.00658972449739389 +/- 0.0015081630007840019</t>
+          <t>0.00018615040953092187 +/- 0.0010693526892289744</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.0014147431124348353 +/- 0.0013505850444688792</t>
+          <t>0.009270290394638881 +/- 0.0018044111416310612</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.0001489203276247353 +/- 0.0010424422933730517</t>
+          <t>3.7230081906186593e-05 +/- 0.0007342919926774417</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.0002606105733432507 +/- 0.0004723967811038435</t>
+          <t>-7.446016381236209e-05 +/- 0.0003245643293775706</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.005882352941176494 +/- 0.0020782257240436128</t>
+          <t>0.0038719285182427453 +/- 0.0013850391092880402</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.006887565152643349 +/- 0.0016753536857781063</t>
+          <t>0.0005956813104989022 +/- 0.00197143742291492</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.0006701414743112477 +/- 0.0010100268031459877</t>
+          <t>-0.0011541325390915735 +/- 0.001097498359864762</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.00011169024571853204 +/- 0.0009277688603408172</t>
+          <t>-0.0003723008190617827 +/- 0.0010661073018076203</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.002010424422933743 +/- 0.0015725027611275368</t>
+          <t>0.005696202531645589 +/- 0.0012465129592541433</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.00029784065524945393 +/- 0.0005471682225129977</t>
+          <t>-0.0010424422933730192 +/- 0.00032456432937755914</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.0025316455696202445 +/- 0.0010100268031459877</t>
+          <t>-0.001154132539091568 +/- 0.0013157555507872145</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.001154132539091568 +/- 0.0015480731858742922</t>
+          <t>0.0031645569620253333 +/- 0.001581730885051977</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.0010424422933730305 +/- 0.0016633140657996077</t>
+          <t>0.004988830975428155 +/- 0.0013131192917757598</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.006850335070737174 +/- 0.001434204042014758</t>
+          <t>0.001451973194341033 +/- 0.0014840753110941748</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.0005584512285927157 +/- 0.0005063838610847265</t>
+          <t>-0.0004467609828741448 +/- 0.0004341736332721604</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>7.446016381236209e-05 +/- 0.00032456432937757063</t>
+          <t>-0.0004095309009679693 +/- 0.0003886934664523504</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.005658972449739408 +/- 0.0006405305485512155</t>
+          <t>0.003946388682055107 +/- 0.0011069299141711483</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.0013402829486224676 +/- 0.0013444132602582067</t>
+          <t>0.009642591213700685 +/- 0.0019871937669519737</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-0.00018615040953091634 +/- 0.000691518079709853</t>
+          <t>-0.0017870439314966347 +/- 0.0007408692755820124</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.0017498138495904536 +/- 0.0004095309009679915</t>
+          <t>-3.723008190615884e-05 +/- 0.0006955153273369033</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.00014892032762474637 +/- 0.00143420404201477</t>
+          <t>0.0015636634400595707 +/- 0.0012437299395748396</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.00383469843633657 +/- 0.0013531483131337466</t>
+          <t>0.002792256142963534 +/- 0.0010822369213513558</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.0001116902457185598 +/- 0.001246512959254155</t>
+          <t>0.00026061057334327286 +/- 0.0005008795252075099</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.004914370811615804 +/- 0.0014591152600346568</t>
+          <t>0.003909158600148938 +/- 0.0021076961808962264</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.008749069247952362 +/- 0.0019147268608523868</t>
+          <t>0.007855547282204039 +/- 0.0010324217888207149</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.0008190618019359774 +/- 0.0017044710561816257</t>
+          <t>0.0022338049143708293 +/- 0.0009119470375216601</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.004877140729709623 +/- 0.0012058179255920874</t>
+          <t>0.0035368577810871325 +/- 0.001180258189437635</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.00673864482501863 +/- 0.0026611045835455596</t>
+          <t>-0.0002233804914370696 +/- 0.0017870439314966494</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.0017125837676843115 +/- 0.0008683472665443489</t>
+          <t>-0.00014892032762470753 +/- 0.0016995848414762937</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.007408786299329872 +/- 0.0013262481854472725</t>
+          <t>0.0017870439314966625 +/- 0.0013709570096442252</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.0013775130305286932 +/- 0.0005534649570855776</t>
+          <t>-0.0005584512285926934 +/- 0.0005330536509037995</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0016753536857780972 +/- 0.001385539394335694</t>
+          <t>0.00573343261355177 +/- 0.0016415046675389848</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.0013775130305286986 +/- 0.0018987341772151907</t>
+          <t>0.002568875651526448 +/- 0.001987193766951976</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.010759493670886095 +/- 0.0012285927029039457</t>
+          <t>0.0011913626209977823 +/- 0.0015601136887384258</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.011131794489947899 +/- 0.0018273106763675411</t>
+          <t>0.005249441548771422 +/- 0.0017577172947301348</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-0.000819061801935983 +/- 0.00043417363327218425</t>
+          <t>0.00037230081906181045 +/- 0.0003329959758004231</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>-0.0010424422933730637 +/- 0.001114417687795665</t>
+          <t>0.0008935219657483451 +/- 0.00024695642519400414</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-0.00033507073715563496 +/- 0.0006544451165765861</t>
+          <t>3.7230081906181044e-05 +/- 0.0002606105733432673</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.004728220402084898 +/- 0.0012353432630705127</t>
+          <t>-0.0015636634400595483 +/- 0.0011390214847936163</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.0071109456440804405 +/- 0.0013262481854472681</t>
+          <t>-0.0050632911392405 +/- 0.0021270077225742003</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-0.0005212211466865402 +/- 0.0008019605073915962</t>
+          <t>-0.0008562918838421196 +/- 0.0005534649570855728</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.006254653760238288 +/- 0.001139021484793626</t>
+          <t>0.0036485480268056815 +/- 0.0015422423810281512</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.0037230081906180377 +/- 0.002039175567777983</t>
+          <t>0.0016008935219657572 +/- 0.0014989443141621408</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.0006329113924050444 +/- 0.0007993637585101925</t>
+          <t>-0.0014147431124348297 +/- 0.0007024557804956596</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.0016753536857781303 +/- 0.0011075558287895434</t>
+          <t>0.0011541325390915958 +/- 0.0013366584565164708</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.007967237527922588 +/- 0.0018851807745602664</t>
+          <t>0.0004839910647803536 +/- 0.0012685573371110047</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.0052122114668652405 +/- 0.001441914872005747</t>
+          <t>0.0018615040953090245 +/- 0.0014514958071197355</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.015562174236783332 +/- 0.001391030654673832</t>
+          <t>-0.0013402829486224787 +/- 0.0010556550170333502</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>-7.446016381236209e-05 +/- 0.00043417363327218425</t>
+          <t>-0.0002978406552494317 +/- 0.0003245643293775477</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.007446016381236065 +/- 0.0010397796011741578</t>
+          <t>-0.0033134772896500297 +/- 0.0016770075397699463</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.0015636634400595872 +/- 0.0011390214847936282</t>
+          <t>0.002047654504839924 +/- 0.0013449286573483546</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.0006329113924050777 +/- 0.0005278275085166846</t>
+          <t>-0.0019359642591213588 +/- 0.0005956813104988967</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.0058823529411764774 +/- 0.0016716265316934998</t>
+          <t>0.0007446016381236154 +/- 0.0016897700250052478</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.0032762472077438763 +/- 0.0008122644910376538</t>
+          <t>-0.0011169024571853925 +/- 0.0011292442954656016</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-0.015562174236783338 +/- 0.001276725852530317</t>
+          <t>-0.003052866716306768 +/- 0.001560113688738413</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-0.00018615040953091078 +/- 0.0003814948163052669</t>
+          <t>-0.0001861504095308941 +/- 0.0004162449697505089</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.0004709274251926036</t>
+          <t>-0.0003723008190617827 +/- 0.0006659919516008243</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.0021221146686522642 +/- 0.0009996814283021159</t>
+          <t>-0.001563663440059554 +/- 0.0007408692755820008</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.00026061057334327844 +/- 0.0008165194415287208</t>
+          <t>0.00033507073715563496 +/- 0.0010052122114668617</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.011131794489947893 +/- 0.0014652768915975121</t>
+          <t>0.001675353685778125 +/- 0.0012707407420607553</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.0014519731943410496 +/- 0.0006329113924050641</t>
+          <t>0.00037230081906181045 +/- 0.000440512269776601</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.004058078927773656 +/- 0.0015747048386118043</t>
+          <t>-0.002233804914370796 +/- 0.0014610139143967694</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>-0.006180193596425932 +/- 0.0023082650781831786</t>
+          <t>-0.0002606105733432451 +/- 0.00153548701618029</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.0009307520476545261 +/- 0.0006501954280183687</t>
+          <t>0.0007073715562174343 +/- 0.0006329113924050676</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>-0.01023827252419957 +/- 0.0009004755489536828</t>
+          <t>-0.004430379746835428 +/- 0.0006752925222344458</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>-0.015897244973938955 +/- 0.0016060800156457893</t>
+          <t>-0.007632166790766925 +/- 0.0010949695584402661</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.0022338049143708293 +/- 0.0016566340626423637</t>
+          <t>-0.001638123603871927 +/- 0.0010017590504150212</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.0005625879043600124 +/- 0.001146941380471178</t>
+          <t>-0.0003164556962024778 +/- 0.001436476667778856</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0013009845288326604 +/- 0.0022296538484511377</t>
+          <t>0.0010196905766526431 +/- 0.0013658878058758937</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.000738396624472526 +/- 0.0015119549929676443</t>
+          <t>0.0023206751054852814 +/- 0.001372659725453112</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0007735583684951198 +/- 0.0016921532229980246</t>
+          <t>-0.0034810126582278 +/- 0.0014535883690994812</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.01090014064697612 +/- 0.0012967010488457048</t>
+          <t>-0.0009845288326300384 +/- 0.001473440706030736</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0065752461322081904 +/- 0.0034019782333155465</t>
+          <t>0.003727144866385412 +/- 0.0017942828160581114</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0002812939521800395 +/- 0.00034451332528597433</t>
+          <t>3.3306690738754695e-17 +/- 0.000351617440225005</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.005133614627285532 +/- 0.0016877637130801703</t>
+          <t>0.0014416315049226914 +/- 0.002237403413492684</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.028832630098452917 +/- 0.0015164457561777675</t>
+          <t>0.017791842475386833 +/- 0.0032728765902166187</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.017932489451476817 +/- 0.0035231997327356706</t>
+          <t>0.020534458509142095 +/- 0.0035063152917912638</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-0.001230661040787584 +/- 0.0016660137469032413</t>
+          <t>-0.0014064697609000865 +/- 0.001693613864809047</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.003973277074542913 +/- 0.0012971776895707998</t>
+          <t>-0.0012306610407875728 +/- 0.0012604394042851621</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.010970464135021119 +/- 0.0018658929903546545</t>
+          <t>7.032348804504318e-05 +/- 0.0018725073074113124</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.042475386779184277 +/- 0.0033791881228506155</t>
+          <t>0.0476441631504923 +/- 0.004386771067389868</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.029571026722925508 +/- 0.003018385363151339</t>
+          <t>0.042018284106891735 +/- 0.003804136719526674</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.009106891701828445 +/- 0.0012426580201879342</t>
+          <t>0.0026722925457103087 +/- 0.0017873790474175657</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.0064345991561181705 +/- 0.0013254625052722098</t>
+          <t>0.0073488045007032874 +/- 0.0013838726198420795</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.006610407876230673 +/- 0.001465025784528802</t>
+          <t>-0.0003164556962024778 +/- 0.0011279194748484787</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.002180028129395173 +/- 0.0008867454439464503</t>
+          <t>0.00407876230661045 +/- 0.002224935586435501</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.000351617440225005 +/- 0.000351617440225005</t>
+          <t>7.032348804503208e-05 +/- 0.00030653297774545815</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.0025668073136427714 +/- 0.00162696699033181</t>
+          <t>0.007067510548523259 +/- 0.0017329425499791249</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0029887482419128308 +/- 0.0016132306254506832</t>
+          <t>-0.000668073136427505 +/- 0.0013749096199730903</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.004360056258790446 +/- 0.0016804223833120264</t>
+          <t>0.004395218002812984 +/- 0.0019210672826508633</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.0009142053445850617 +/- 0.0011029808116285605</t>
+          <t>0.0023206751054852593 +/- 0.0013268609187139938</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.0011954992967650902 +/- 0.0011251758087201227</t>
+          <t>-0.0019690576652601653 +/- 0.0011141335807141246</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.00017580872011252469 +/- 0.0003241752622114367</t>
+          <t>0.0008438818565401184 +/- 0.0005262527970146402</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-0.0016526019690576543 +/- 0.0019893593755015092</t>
+          <t>0.009845288326301016 +/- 0.002240440551627859</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.0019690576652601653 +/- 0.0007409039207351031</t>
+          <t>-0.002566807313642716 +/- 0.0015330681685366816</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.0013009845288326604 +/- 0.0017584387834106794</t>
+          <t>4.4408920985006264e-17 +/- 0.001483475605466165</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.0033755274261603185 +/- 0.001581887746723199</t>
+          <t>-0.009950773558368476 +/- 0.001751393727906093</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-0.0009845288326300605 +/- 0.0005625879043600415</t>
+          <t>-0.00035161744022499386 +/- 0.0009033215596810853</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.00024613220815749014 +/- 0.0004730528849181798</t>
+          <t>-0.0006329113924050112 +/- 0.0006634304593569878</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.0015822784810126333 +/- 0.0015822784810126654</t>
+          <t>-0.006504922644163113 +/- 0.001702714488439277</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.0014767932489451075 +/- 0.0013043063988038978</t>
+          <t>0.0005625879043600901 +/- 0.002075436647450601</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-0.00010548523206749261 +/- 0.0004461525154869616</t>
+          <t>0.003445850914205362 +/- 0.0010525055940292538</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.00024613220815754565 +/- 0.0007549546608152025</t>
+          <t>-0.000703234880450021 +/- 0.0006854285755843088</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.0017932489451476298 +/- 0.0017752328496996228</t>
+          <t>-0.000703234880450021 +/- 0.002337661060280541</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>-0.0027426160337552406 +/- 0.001617440225035146</t>
+          <t>-0.005485232067510515 +/- 0.0018751465015433653</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.00021097046413499633 +/- 0.0006708433202650665</t>
+          <t>0.0011603375527426628 +/- 0.0006299744327415486</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.003059071729957774 +/- 0.0013254625052722116</t>
+          <t>0.0004571026722926086 +/- 0.001228650155390729</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0016877637130801927 +/- 0.0016020795710118864</t>
+          <t>0.002180028129395284 +/- 0.001735437788924472</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.0010196905766525655 +/- 0.001789107487089818</t>
+          <t>0.007946554149085839 +/- 0.0025752227037412947</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.0027074542897328026 +/- 0.0017157345849164243</t>
+          <t>-0.007700421940928237 +/- 0.00123266864577764</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>-0.002707454289732736 +/- 0.0014922007857892344</t>
+          <t>-0.00014064697608996425 +/- 0.0014514604388572525</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.004676511954993012 +/- 0.0007383966244725609</t>
+          <t>0.003305203938115364 +/- 0.001372659725453107</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.000351617440225005 +/- 0.0013887776130894274</t>
+          <t>0.001863572433192706 +/- 0.0012876113518706428</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.0006680731364275161 +/- 0.0006754350461426941</t>
+          <t>-0.0003867791842474766 +/- 0.0005977496483825427</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>-0.000738396624472537 +/- 0.0008818520537260411</t>
+          <t>0.001125175808720158 +/- 0.0009408641462911154</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.006258790436005657 +/- 0.002341888298923588</t>
+          <t>-0.003551336146272799 +/- 0.001607087887767433</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.002812939521800262 +/- 0.002240440551627859</t>
+          <t>-0.00861462728551331 +/- 0.0014772117818284286</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.002531645569620278 +/- 0.0020002057177676376</t>
+          <t>-0.005625879043600501 +/- 0.0013618084902276523</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.0001758087201124803 +/- 0.0010922802086504278</t>
+          <t>-0.00042194092826999265 +/- 0.0009276305174594139</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>-0.0010196905766525655 +/- 0.0006754350461426941</t>
+          <t>0.0003516174402250716 +/- 0.0007541353934432911</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0005625879043600679 +/- 0.0008201057517363318</t>
+          <t>-7.032348804498767e-05 +/- 0.0002631263985072816</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.0045007032348804545 +/- 0.0018525935122812294</t>
+          <t>0.005203938115330542 +/- 0.0011096859239141715</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.0016526019690576322 +/- 0.0015491132750992</t>
+          <t>0.0022151898734177667 +/- 0.0016193500618381777</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0014767932489450964 +/- 0.0004100528758681812</t>
+          <t>-0.00017580872011246917 +/- 0.000527426160337526</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.005414908579465494 +/- 0.0017665058631618142</t>
+          <t>0.002461322081575279 +/- 0.0012481180977003477</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.003938115330520376 +/- 0.0022722214376095034</t>
+          <t>-0.006962025316455645 +/- 0.002404405203555381</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>-0.0012658227848100778 +/- 0.0010335399758579018</t>
+          <t>-0.0006680731364275161 +/- 0.0007450639979049507</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.0043248945147679515 +/- 0.0013892226628085974</t>
+          <t>0.0031997187060478606 +/- 0.0014872212364667081</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.0022151898734177667 +/- 0.0018273961266084824</t>
+          <t>-0.01592827004219406 +/- 0.001441631504922652</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-0.006821378340365658 +/- 0.0014851414966204491</t>
+          <t>0.0016526019690577098 +/- 0.0012286501553907183</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-0.0015471167369901285 +/- 0.00099700751608705</t>
+          <t>0.002109704641350252 +/- 0.0009693423876294015</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>-0.00014064697609000865 +/- 0.0002812939521800173</t>
+          <t>0.00024613220815753454 +/- 0.00022514501538091095</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.000386779184247521 +/- 0.0013476630025834515</t>
+          <t>-0.0013009845288325828 +/- 0.0011344772014698743</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.0003867791842475654 +/- 0.0015362905959882777</t>
+          <t>0.00035161744022509377 +/- 0.001423942104874576</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.0005274261603375075 +/- 0.0007076164485758673</t>
+          <t>-0.002180028129395173 +/- 0.0007830892212137852</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.004008438818565441 +/- 0.0016730488401364852</t>
+          <t>0.003762306610407928 +/- 0.0018341492764760868</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0.0031997187060478494 +/- 0.0012426580201879245</t>
+          <t>-0.0006329113924050222 +/- 0.0016020795710118831</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-7.032348804497657e-05 +/- 0.001265822784810115</t>
+          <t>-0.0008438818565400297 +/- 0.001189278096011784</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>-7.032348804500988e-05 +/- 0.00014064697609001976</t>
+          <t>0.00014064697609003085 +/- 0.0002332366237943179</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.0007735583684951086 +/- 0.000562587904360079</t>
+          <t>-0.0008438818565400297 +/- 0.0005925562428393987</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.0006680731364275272 +/- 0.0006377762709991787</t>
+          <t>-0.00024613220815745686 +/- 0.0002746219998560378</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.0016526019690577098 +/- 0.0007383966244725741</t>
+          <t>-0.0007735583684950309 +/- 0.0010406925869865524</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.004254571026722942 +/- 0.0017960046116908654</t>
+          <t>-0.004395218002812895 +/- 0.001695437897502284</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4396,37 +4396,37 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0004160393659001305</t>
+          <t>0.0005625879043600901 +/- 0.000526252797014621</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0026371308016878035 +/- 0.0007743570866928616</t>
+          <t>-0.0016526019690576098 +/- 0.001177262239295581</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.0004571026722925864 +/- 0.0017863411808552035</t>
+          <t>-0.003059071729957774 +/- 0.001433029808179673</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.0002109704641350074 +/- 0.0004219409282700241</t>
+          <t>-0.0015119549929676012 +/- 0.00044615251548699137</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>-0.0005977496483825173 +/- 0.0013713080168776476</t>
+          <t>0.0003867791842475765 +/- 0.0015037556104320045</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.003270042194092848 +/- 0.0015728740679567556</t>
+          <t>0.00597749648382564 +/- 0.0020381683187326955</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>-0.0005625879043600013 +/- 0.000878340084162917</t>
+          <t>-0.0036568213783403137 +/- 0.0007574071458698326</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.004800268546492148 +/- 0.001072611299675773</t>
+          <t>-0.0023833501174891137 +/- 0.0012953193273967489</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.018865391070829185 +/- 0.00183738599307205</t>
+          <t>-0.01785834172541122 +/- 0.0006680009648248282</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.00896273917421958 +/- 0.0012200592041212795</t>
+          <t>-0.0010741859684458067 +/- 0.0013905548960864865</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0049009734810338546 +/- 0.001998372080045271</t>
+          <t>0.009768378650553865 +/- 0.0018167249584068257</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.011043974488083308 +/- 0.0007720711648203963</t>
+          <t>-0.00762000671366232 +/- 0.0017250977049385297</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.0013091641490433515 +/- 0.0015777106411547454</t>
+          <t>-0.009097012420275285 +/- 0.0017146146746051842</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.000503524672708977 +/- 0.00027063637960049615</t>
+          <t>-0.0007385028533064997 +/- 0.00025120224147526335</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.009466263846928547 +/- 0.0007915291119538054</t>
+          <t>-0.008291372943940934 +/- 0.0007807790097088511</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.032829808660624314 +/- 0.0028317014714955655</t>
+          <t>0.02356495468277945 +/- 0.003645833899264312</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.04394091977173541 +/- 0.0037842967662597583</t>
+          <t>0.040718361866398115 +/- 0.004182051207205431</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.005135951661631366 +/- 0.001351515417200229</t>
+          <t>0.0070829137294394105 +/- 0.0015633609966021998</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.007854984894259875 +/- 0.0012931426844080677</t>
+          <t>-0.003625377643504546 +/- 0.0009470786156203988</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.006277274253105125 +/- 0.0014712727090171883</t>
+          <t>-0.0002685464921114433 +/- 0.00212728828704329</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.025142665323934155 +/- 0.0018167249584068207</t>
+          <t>0.027223900637797893 +/- 0.002182972875178127</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.00043638804968104683 +/- 0.00234041195213875</t>
+          <t>0.001644847264182614 +/- 0.0017600170163032337</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.0006377979187646377 +/- 0.0011863442126265357</t>
+          <t>0.002819738167170194 +/- 0.001827547175403323</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.005102383350117534 +/- 0.0012084592145015258</t>
+          <t>-0.001980530379321921 +/- 0.0016475852556976228</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.002685464921114422 +/- 0.0013343139922357796</t>
+          <t>-0.006579389056730467 +/- 0.001052996786932389</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.009197717354817104 +/- 0.0014098690835851134</t>
+          <t>-0.002987579724739864 +/- 0.0016407317099496456</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-3.3568311513942904e-05 +/- 0.00027883933745946545</t>
+          <t>-0.00036925142665324986 +/- 0.00035046346119203917</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.01037260825780456 +/- 0.0017600170163032424</t>
+          <t>0.013225914736488754 +/- 0.0014178390118793468</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.0038603558241020798 +/- 0.001155549813901195</t>
+          <t>-0.008660624370594183 +/- 0.0008465606050969352</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0005035246727089105 +/- 0.0013022601370440295</t>
+          <t>-0.0026854649211144888 +/- 0.000497898522127909</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.00023497818059747821 +/- 0.0009734810339039794</t>
+          <t>-0.0013091641490433291 +/- 0.00107680529925113</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.0026518966096006013 +/- 0.0008811282140588614</t>
+          <t>-0.003726082578046341 +/- 0.001548878414912304</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.00016784155756969233 +/- 0.0004311927686694977</t>
+          <t>-0.0010741859684458178 +/- 0.0004699563611950453</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>-0.01067472306143007 +/- 0.0025906386547935208</t>
+          <t>-0.012420275260154445 +/- 0.002175475226051652</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.010506881503860411 +/- 0.0014403113764971513</t>
+          <t>-0.01584424303457539 +/- 0.002200197329059944</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>-0.006646525679758364 +/- 0.001208459214501513</t>
+          <t>-0.010137630077207138 +/- 0.0011113088524502626</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.007250755287009114 +/- 0.0013018274205884631</t>
+          <t>-0.015273581738838549 +/- 0.001449669209915361</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.00023497818059755592 +/- 0.0009013576087342901</t>
+          <t>0.00036925142665324986 +/- 0.0004614879853933504</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.0009063444108761698 +/- 0.0005627074392158428</t>
+          <t>-0.0008392077878482951 +/- 0.0004806250776527949</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.004632426988922511 +/- 0.0011113088524502652</t>
+          <t>-0.013326619671030559 +/- 0.0014865115693511054</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.011480362537764388 +/- 0.0013824276792194635</t>
+          <t>-0.009298422289358876 +/- 0.0008091286198854693</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-0.0005035246727089881 +/- 0.0005035246727089511</t>
+          <t>-0.0005706612957368407 +/- 0.00033735735552605493</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.0007049345417924679 +/- 0.0005296990210828902</t>
+          <t>-0.0006377979187647042 +/- 0.0004363880496811134</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.00040281973816721497 +/- 0.0012361163235664267</t>
+          <t>-0.0036589459550184665 +/- 0.0013381088572000357</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>-0.004095334004699613 +/- 0.001037907004614972</t>
+          <t>-0.0070829137294394105 +/- 0.0009895537410529425</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.0005370929842228201 +/- 0.0009518259065966936</t>
+          <t>-0.0013427324605572721 +/- 0.000561705288039006</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.00046995636119496754 +/- 0.0008518682470929316</t>
+          <t>-0.003625377643504546 +/- 0.0013660281939829387</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.00540449815374291 +/- 0.0013039895669389046</t>
+          <t>-0.006579389056730467 +/- 0.0014178390118793375</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.005471634776770784 +/- 0.0007513604996844325</t>
+          <t>-0.009164149043303139 +/- 0.0014403113764971513</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.004028197381671761 +/- 0.001308733715315059</t>
+          <t>-0.0080563947633434 +/- 0.0014399201469974835</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.00013427324605577162 +/- 0.0007073282143573255</t>
+          <t>-0.00013427324605572722 +/- 0.0009518259065967256</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.0016784155756965902 +/- 0.0010508543700905656</t>
+          <t>-0.001174890902987602 +/- 0.0008913003052938386</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.003994629070157807 +/- 0.001822916949632159</t>
+          <t>-0.002954011413225921 +/- 0.0006846619017915582</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-0.00016784155756968122 +/- 0.0005254271850452473</t>
+          <t>-0.00026854649211145444 +/- 0.00025120224147526335</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>-0.0014770057066130105 +/- 0.0012214437998429323</t>
+          <t>0.001174890902987591 +/- 0.0011057179652232709</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.003692514266532465 +/- 0.001072085896117559</t>
+          <t>-0.008291372943940934 +/- 0.0013431519989085268</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.003121852970795613 +/- 0.0015676796816160613</t>
+          <t>-0.005605908022826467 +/- 0.0019460937281820306</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.0059080228264518754 +/- 0.0012843992258952084</t>
+          <t>-0.005538771399798604 +/- 0.0016462168291694235</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.00045036615861020104</t>
+          <t>0.0005706612957368295 +/- 0.0006014257424360064</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>-0.0007385028533065108 +/- 0.0005576786749189656</t>
+          <t>0.00026854649211145444 +/- 0.0002926417551890431</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.0009734810339039113 +/- 0.00023497818059752264</t>
+          <t>-0.0024504867405169884 +/- 0.0002621768941223754</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.0018462571332662381 +/- 0.0018030277276932917</t>
+          <t>-0.0027526015441423413 +/- 0.0016971097226941353</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.002081235313863761 +/- 0.0011214026914058545</t>
+          <t>-0.008358509566968797 +/- 0.0017277085239956827</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0.0005370929842228089 +/- 0.00037380089713526644</t>
+          <t>-0.0013763007720712039 +/- 0.0006788770868129325</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>0.0021483719368915466 +/- 0.0020040028944745616</t>
+          <t>-0.00013427324605574942 +/- 0.0013775283335806122</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.004665995300436432 +/- 0.0010975349261008246</t>
+          <t>-0.006176569318563263 +/- 0.0018027152174686237</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>-0.00033568311513934026 +/- 0.0007041348426788413</t>
+          <t>-0.00016784155756965902 +/- 0.00030948454035895095</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.000872776099362238 +/- 0.0011353833182469232</t>
+          <t>-0.0012084592145015117 +/- 0.0014257643894995098</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.004800268546492159 +/- 0.0017510307292037453</t>
+          <t>-0.009063444108761342 +/- 0.0017951986515100172</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.006143001007049287 +/- 0.000961836104860321</t>
+          <t>-0.0002685464921114766 +/- 0.001280885131140578</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-0.00036925142665330537 +/- 0.0014819563648636464</t>
+          <t>0.00043638804968109123 +/- 0.0017053891635959203</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>-4.4408920985006264e-17 +/- 0.00042460928636027425</t>
+          <t>-0.0002349781805975226 +/- 0.0002621768941224195</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.0018126888217522175 +/- 0.0020152173239078425</t>
+          <t>-0.007922121517287684 +/- 0.0013190253577971447</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.0013091641490432515 +/- 0.0013039895669389198</t>
+          <t>0.0021483719368915687 +/- 0.0014952035885411232</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.0008727760993621269 +/- 0.0006404425655702806</t>
+          <t>0.001477005706612966 +/- 0.0006912138396097179</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.003826787512588048 +/- 0.0016112789526686836</t>
+          <t>0.009634105404498139 +/- 0.0016854501793398084</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>-0.0016784155756966012 +/- 0.0012103226839422748</t>
+          <t>-0.0059415911379657625 +/- 0.0012918349382271756</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-0.0013427324605572721 +/- 0.0018447306698938174</t>
+          <t>0.0036253776435045126 +/- 0.0018312429267520478</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>0.0003021148036253085 +/- 0.0002349781805974798</t>
+          <t>-3.3568311513931805e-05 +/- 0.00031668281745743105</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>-0.00040281973816720386 +/- 0.0008331435814696731</t>
+          <t>-0.000503524672708977 +/- 0.0009524176541867413</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-6.713662302788581e-05 +/- 0.0005576786749189508</t>
+          <t>-3.356831151395401e-05 +/- 0.0010975349261008233</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,52 +4826,52 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-0.0006042296072507946 +/- 0.0006680009648248361</t>
+          <t>-0.0005370929842229089 +/- 0.000524353788244839</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.00020140986908352422 +/- 0.0008385361528564259</t>
+          <t>0.0026183282980866028 +/- 0.001670339752215474</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.0001342732460556828 +/- 0.00016445046947179842</t>
+          <t>-0.0006042296072507724 +/- 0.00020140986908359081</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>3.356831151388739e-05 +/- 0.0006788770868128908</t>
+          <t>0.00033568311513931803 +/- 0.0004978985221279539</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-0.005505203088284716 +/- 0.0010846253387984956</t>
+          <t>-0.0037260825780463303 +/- 0.0009665109129834229</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.0009734810339039668 +/- 0.001556136554078448</t>
+          <t>0.0020476670023497623 +/- 0.0018596359831439325</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.0013763007720712039 +/- 0.0005505612442718091</t>
+          <t>-0.0013091641490433404 +/- 0.0004614879853933505</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.002215508559919499 +/- 0.0014336459552912178</t>
+          <t>0.0013763007720711596 +/- 0.0013631379996137533</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.0001342732460556717 +/- 0.0009278465902037589</t>
+          <t>-0.0012084592145015117 +/- 0.0013360019296497034</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.004095334004699525 +/- 0.0009229759707866556</t>
+          <t>0.0023162134944612056 +/- 0.0010231453947048051</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0031994776363042598 +/- 0.0011384652807158045</t>
+          <t>0.0014365001632386965 +/- 0.0009371661831150576</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.015279138099902034 +/- 0.001360278593274549</t>
+          <t>0.004505386875612171 +/- 0.0016825463567385075</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.014136467515507633 +/- 0.0018814272979724505</t>
+          <t>0.012993796931113332 +/- 0.0013912684134941378</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.00914136467515505 +/- 0.0014817898423650127</t>
+          <t>-0.002122102513875246 +/- 0.0024223208359842635</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.006496898465556611 +/- 0.001826231311909497</t>
+          <t>0.01632386549134838 +/- 0.001612678946814031</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.00825987593862223 +/- 0.001256407535415856</t>
+          <t>0.003166829905321633 +/- 0.0013543890638388271</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.0006856023506366604 +/- 0.00044883209549026704</t>
+          <t>0.0005876591576885803 +/- 0.00038073469767189755</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.003950375448906263 +/- 0.0011901877984693517</t>
+          <t>0.003754489063010158 +/- 0.0018250636447108975</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.014462944825334601 +/- 0.002865012788695889</t>
+          <t>0.008423114593535785 +/- 0.003756050151686489</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.018217433888344736 +/- 0.003171370406681272</t>
+          <t>0.005419523343127686 +/- 0.002355166672787651</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.019000979431929455 +/- 0.001166214240907065</t>
+          <t>0.02559582109043427 +/- 0.0011042464593723517</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.01472412667319618 +/- 0.0013575333259087101</t>
+          <t>-0.00022853411687883128 +/- 0.0015930620827627592</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.01364675155076719 +/- 0.0010609256813106148</t>
+          <t>0.015507672216780965 +/- 0.0013870483699802772</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.011785830884753467 +/- 0.0017669029223290604</t>
+          <t>0.011655239960822739 +/- 0.002443350602947149</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.02259222984002608 +/- 0.0022229245224354107</t>
+          <t>0.011034933072151499 +/- 0.0013680918602518492</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0035259549461312267 +/- 0.0008361899102099724</t>
+          <t>0.007900750897812647 +/- 0.002094549778954683</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.0005550114267058648 +/- 0.0011408034743490931</t>
+          <t>-0.003134182174338862 +/- 0.0011879468102292004</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.010708455762324477 +/- 0.0014731327682244166</t>
+          <t>0.003983023179889045 +/- 0.0016440977227573312</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.0006529546196539227 +/- 0.0014080221124941395</t>
+          <t>0.00812928501469149 +/- 0.0016156504122309856</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.0001632386549135223 +/- 0.0002632144220796343</t>
+          <t>0.0001632386549135223 +/- 0.00041936769763843516</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.025204048318641824 +/- 0.0018571939475452986</t>
+          <t>0.023571661769507056 +/- 0.0015017956252040363</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.0041136141038197625 +/- 0.0012319923123808656</t>
+          <t>0.014136467515507688 +/- 0.0011775833363938104</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0019588638589617792 +/- 0.0009234172787287629</t>
+          <t>-0.003656545870062 +/- 0.001487533235376378</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.003166829905321611 +/- 0.0008766386929218281</t>
+          <t>-0.006301012079660428 +/- 0.0011684969094465083</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.0014365001632386965 +/- 0.0011879468102292013</t>
+          <t>-0.0006856023506365827 +/- 0.0020774323565044784</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0002611818478616246 +/- 0.00028461632017896766</t>
+          <t>-9.794319294804676e-05 +/- 0.00035912504080966626</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>-0.0016976820111002545 +/- 0.001202216953282545</t>
+          <t>-0.007868103166829876 +/- 0.002107991963089515</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.00976167156382628 +/- 0.001456030239698178</t>
+          <t>-0.01266731962128631 +/- 0.0013365647724752692</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.0021873979758406437 +/- 0.001256407535415856</t>
+          <t>0.003754489063010169 +/- 0.0008544728911722351</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.0013712047012732985 +/- 0.0014731327682244138</t>
+          <t>0.007704864511916465 +/- 0.0019490449306691787</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0006529546196539004 +/- 0.0003576379742116696</t>
+          <t>3.264773098273777e-05 +/- 0.0004244205027750615</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.0002611818478616357 +/- 0.00013059092393081782</t>
+          <t>0.0006529546196539892 +/- 0.00035763797421164934</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,272 +5051,272 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.264773098267115e-05 +/- 0.0015134609189029454</t>
+          <t>0.004048318641854421 +/- 0.0022486680192912102</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.000816193274567445 +/- 0.0012324248180330761</t>
+          <t>-0.014626183480248078 +/- 0.0017014448868162505</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.0005223636957231159 +/- 0.0003635497461854412</t>
+          <t>0.0003917727717924091 +/- 0.0004570682337577657</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.0006856023506365938 +/- 0.0004940498188188691</t>
+          <t>3.264773098273777e-05 +/- 0.0008056782683156054</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.0042442050277505805 +/- 0.0008259295227341626</t>
+          <t>-0.0043095004897159336 +/- 0.001473132768224428</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.006627489389487396 +/- 0.0015930620827627733</t>
+          <t>0.0013059092393079119 +/- 0.0013927998046164955</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.001436500163238641 +/- 0.0008023640696992912</t>
+          <t>-0.0004570682337577292 +/- 0.0008662421914085316</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>9.794319294805786e-05 +/- 0.001460415882882489</t>
+          <t>-0.006953966699314362 +/- 0.0017944376211115076</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.006007182500816177 +/- 0.0013317713388423975</t>
+          <t>0.0007182500816193648 +/- 0.001473132768224429</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-0.0006856023506366604 +/- 0.0008444346821010314</t>
+          <t>-0.007770159973881774 +/- 0.0011003786840582948</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0017956252040483012 +/- 0.0016143304361836324</t>
+          <t>-0.003721841332027365 +/- 0.0016723798204199502</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>-0.0015670910871694588 +/- 0.000823344447464492</t>
+          <t>-0.010773751224289863 +/- 0.001168040732614984</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.0002285341168789201 +/- 0.0005664169628761744</t>
+          <t>0.007606921318968373 +/- 0.001239324381071009</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.0014691478942213897 +/- 0.0009601985745904592</t>
+          <t>0.00395037544890634 +/- 0.0009053493061614287</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.0002611818478615802 +/- 0.0006496816435563771</t>
+          <t>6.529546196544222e-05 +/- 0.0005223636957231631</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.0009794319294808783 +/- 0.001011552947099547</t>
+          <t>0.004668625530525683 +/- 0.0018814272979724308</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.002122102513875268 +/- 0.0014398352641984908</t>
+          <t>-0.005746000652954597 +/- 0.0010241193040390504</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.00029382957884424024 +/- 0.0011351837186231756</t>
+          <t>0.0025465230166503705 +/- 0.001995521618013218</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.00568070519098921 +/- 0.0020241593209271934</t>
+          <t>-0.002481227554684928 +/- 0.0014832277755926406</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-9.794319294811337e-05 +/- 0.0003591250408096683</t>
+          <t>-0.00022853411687883128 +/- 0.0005068290792118927</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0001632386549135223 +/- 0.00041936769763843516</t>
+          <t>-0.0012732615083251187 +/- 0.000448832095490288</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>-6.529546196538671e-05 +/- 0.00019588638589616015</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>-0.0013712047012732099 +/- 0.002573999783797201</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-0.0017956252040482678 +/- 0.001161176574846787</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>3.2647730982682256e-05 +/- 0.0018320584847010368</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.012112308194580434 +/- 0.0013337706964293497</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>0.0012079660463598318 +/- 0.0006203068886712427</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>0.000718250081619376 +/- 0.0007270994923708803</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>0.00019588638589620455 +/- 0.0016007379264944587</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.0013385569702906053 +/- 0.000535462600942095</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-0.0020568070519098704 +/- 0.001823895229965856</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>0.0005876591576885915 +/- 0.002586392728741548</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>0.009435194253999357 +/- 0.0016483063090257117</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-0.004146261834802445 +/- 0.0018983469487569903</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0.000391772771792398 +/- 0.00040777002927837964</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0.006986614430297133 +/- 0.0014760241012676805</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0.0006856023506366827 +/- 0.0008693128929607781</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>-0.002317988899771417 +/- 0.0008814887365328287</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0.01061051256937644 +/- 0.0013638001027884727</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>-0.0010120796604635607 +/- 0.0010267179362400429</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>0.009076069213189708 +/- 0.0011100228534116955</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>0.0013385569702905943 +/- 0.0007219505186906886</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>-9.794319294804676e-05 +/- 0.0005472756974939765</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0.001403852432255992 +/- 0.000786939000535031</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>-6.529546196538671e-05 +/- 0.00013059092393077342</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>0.00035912504080971576 +/- 0.0006917930166639686</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>0.002415932092719597 +/- 0.0012745165717233426</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>0.0009794319294808783 +/- 0.000584020366307489</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>0.005256284688214152 +/- 0.0008188009274557236</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>0.0063989552726085195 +/- 0.0013789560615045837</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.0002285341168788535 +/- 0.0004142532660936846</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.0030035912504080666 +/- 0.0007416138877963063</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>0.0020894547828925634 +/- 0.001497531170901695</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>0.0010447273914462652 +/- 0.0011290640852621916</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>0.004766568723473708 +/- 0.0010447273914462958</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>-0.0002938295788443068 +/- 0.0002711924212510185</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>-0.002252693437806075 +/- 0.0010267179362400596</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>-0.00192621612797913 +/- 0.0009170468106554576</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>-0.0018609206660137434 +/- 0.0005664169628762077</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0.007770159973881807 +/- 0.0018340936213108961</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>-0.0003264773098270113 +/- 0.0003576379742116697</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>-0.0003264773098269891 +/- 0.0014817898423650079</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>3.2647730982693356e-05 +/- 9.794319294808007e-05</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>-0.0006203068886712737 +/- 0.00034085231827979433</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0.0001305909239307401 +/- 0.00036354974618544515</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>-0.0008488410055501383 +/- 0.00044285536944989876</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>0.0013385569702905498 +/- 0.00112575511913593</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-0.00029382957884429575 +/- 0.0003408523182798219</t>
+          <t>-0.00032647730982691134 +/- 0.00038629316246161183</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.0009794319294809228 +/- 0.000825929522734123</t>
+          <t>-0.0037871367939927847 +/- 0.0025170532507210346</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.0006529546196539004 +/- 0.0010528576883184514</t>
+          <t>0.01093698987920343 +/- 0.0016143304361835998</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>-0.000816193274567456 +/- 0.0005314665555370149</t>
+          <t>-0.0014038524322559254 +/- 0.0008265745283168053</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.0019262161279791413 +/- 0.0006099099475112534</t>
+          <t>0.009304603330068606 +/- 0.001161176574846787</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.010316682990532122 +/- 0.0023687048184416583</t>
+          <t>0.010251387528566802 +/- 0.0017101927330994183</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>-0.0013712047012732875 +/- 0.0005803587605168613</t>
+          <t>0.005582761998041174 +/- 0.0011445346485771022</t>
         </is>
       </c>
     </row>
